--- a/Warehouse_Operations_Simulation.xlsx
+++ b/Warehouse_Operations_Simulation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Upgrade skill\1. Excel - Data Analytics\Project\Warehouse Operations Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AEE89B-4558-4D5B-BC50-C5B24B15010F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101C287A-8C0B-4552-8526-2818462A53FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="500" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Master_Material" sheetId="1" r:id="rId1"/>

--- a/Warehouse_Operations_Simulation.xlsx
+++ b/Warehouse_Operations_Simulation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Upgrade skill\1. Excel - Data Analytics\Project\Warehouse Operations Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101C287A-8C0B-4552-8526-2818462A53FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F2099E-64D3-4BAD-8293-D3720A51B8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Warehouse_Operations_Simulation.xlsx
+++ b/Warehouse_Operations_Simulation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Upgrade skill\1. Excel - Data Analytics\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCE9EDA-58C1-4B85-89F9-A2C1EE49C6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0BB896-0B68-4B93-9E71-6D45D5D9B114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Master_Material" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,9 @@
     <sheet name="11_Cycle_Count" sheetId="11" r:id="rId11"/>
     <sheet name="12_Dashboard" sheetId="12" r:id="rId12"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId13"/>
+  </externalReferences>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -50,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="420">
   <si>
     <t>01_MASTER_MATERIAL  |  Warehouse Operations in a Heavy Equipment Manufacturing Environment</t>
   </si>
@@ -1004,6 +1007,312 @@
   </si>
   <si>
     <t>Remaining quantity awaiting forklift availability</t>
+  </si>
+  <si>
+    <t>07_MATERIAL_REQUEST  |  Warehouse Operations in a Heavy Equipment Manufacturing Environment</t>
+  </si>
+  <si>
+    <t>Request Number</t>
+  </si>
+  <si>
+    <t>Request Line</t>
+  </si>
+  <si>
+    <t>Request Date</t>
+  </si>
+  <si>
+    <t>Required Date</t>
+  </si>
+  <si>
+    <t>Requesting Department</t>
+  </si>
+  <si>
+    <t>Requester</t>
+  </si>
+  <si>
+    <t>Quantity Requested</t>
+  </si>
+  <si>
+    <t>Request Priority</t>
+  </si>
+  <si>
+    <t>Available Stock (Ref)</t>
+  </si>
+  <si>
+    <t>Stock Sufficiency Check</t>
+  </si>
+  <si>
+    <t>Approval Status</t>
+  </si>
+  <si>
+    <t>Total Issued (Ref)</t>
+  </si>
+  <si>
+    <t>Request Status</t>
+  </si>
+  <si>
+    <t>Request Line Key (Helper)</t>
+  </si>
+  <si>
+    <t>MR-2026-0001</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Agung</t>
+  </si>
+  <si>
+    <t>Routine</t>
+  </si>
+  <si>
+    <t>Ini Look up dari stock card</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>MR-2026-0002</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>Bani</t>
+  </si>
+  <si>
+    <t>Machine breakdown - urgent filter replacement</t>
+  </si>
+  <si>
+    <t>MR-2026-0003</t>
+  </si>
+  <si>
+    <t>Rina</t>
+  </si>
+  <si>
+    <t>MR-2026-0004</t>
+  </si>
+  <si>
+    <t>Assembly</t>
+  </si>
+  <si>
+    <t>Dedi</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Awaiting supervisor approval</t>
+  </si>
+  <si>
+    <t>MR-2026-0005</t>
+  </si>
+  <si>
+    <t>Urgent material for production schedule</t>
+  </si>
+  <si>
+    <t>MR-2026-0006</t>
+  </si>
+  <si>
+    <t>Routine preventive maintenance</t>
+  </si>
+  <si>
+    <t>MR-2026-0007</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>Cancelled by requester</t>
+  </si>
+  <si>
+    <t>MR-2026-0008</t>
+  </si>
+  <si>
+    <t>QC</t>
+  </si>
+  <si>
+    <t>Siti</t>
+  </si>
+  <si>
+    <t>MR-2026-0009</t>
+  </si>
+  <si>
+    <t>Production backlog</t>
+  </si>
+  <si>
+    <t>MR-2026-0010</t>
+  </si>
+  <si>
+    <t>Awaiting approval</t>
+  </si>
+  <si>
+    <t>MR-2026-0011</t>
+  </si>
+  <si>
+    <t>Preventive maintenance</t>
+  </si>
+  <si>
+    <t>MR-2026-0012</t>
+  </si>
+  <si>
+    <t>08_PICKING_LIST  |  Warehouse Operations in a Heavy Equipment Manufacturing Environment</t>
+  </si>
+  <si>
+    <t>Pick Number</t>
+  </si>
+  <si>
+    <t>Pick Line</t>
+  </si>
+  <si>
+    <t>Pick Date</t>
+  </si>
+  <si>
+    <t>Requesting Department (Ref)</t>
+  </si>
+  <si>
+    <t>Request Priority (Ref)</t>
+  </si>
+  <si>
+    <t>Quantity Requested (Ref)</t>
+  </si>
+  <si>
+    <t>Pick Location (Ref)</t>
+  </si>
+  <si>
+    <t>Available Stock</t>
+  </si>
+  <si>
+    <t>Quantity Picked</t>
+  </si>
+  <si>
+    <t>Pick Status</t>
+  </si>
+  <si>
+    <t>Picker</t>
+  </si>
+  <si>
+    <t>Pick Line Key (Helper)</t>
+  </si>
+  <si>
+    <t>PL-2026-0001</t>
+  </si>
+  <si>
+    <t>DaDari Stock Card</t>
+  </si>
+  <si>
+    <t>Dari Stock Card</t>
+  </si>
+  <si>
+    <t>PL-2026-0002</t>
+  </si>
+  <si>
+    <t>Dimas</t>
+  </si>
+  <si>
+    <t>Urgent maintenance request</t>
+  </si>
+  <si>
+    <t>PL-2026-0003</t>
+  </si>
+  <si>
+    <t>PL-2026-0004</t>
+  </si>
+  <si>
+    <t>Production replenishment</t>
+  </si>
+  <si>
+    <t>PL-2026-0005</t>
+  </si>
+  <si>
+    <t>PL-2026-0006</t>
+  </si>
+  <si>
+    <t>QC inspection material</t>
+  </si>
+  <si>
+    <t>PL-2026-0007</t>
+  </si>
+  <si>
+    <t>Production priority</t>
+  </si>
+  <si>
+    <t>PL-2026-0008</t>
+  </si>
+  <si>
+    <t>PL-2026-0009</t>
+  </si>
+  <si>
+    <t>PL-2026-0010</t>
+  </si>
+  <si>
+    <t>09_GOODS_ISSUE  |  Warehouse Operations in a Heavy Equipment Manufacturing Environment</t>
+  </si>
+  <si>
+    <t>GI Number</t>
+  </si>
+  <si>
+    <t>GI Line</t>
+  </si>
+  <si>
+    <t>GI Date</t>
+  </si>
+  <si>
+    <t>Issuing Location (Ref)</t>
+  </si>
+  <si>
+    <t>Quantity Picked (Ref)</t>
+  </si>
+  <si>
+    <t>Quantity Issued</t>
+  </si>
+  <si>
+    <t>Issue Variance</t>
+  </si>
+  <si>
+    <t>Issue Status</t>
+  </si>
+  <si>
+    <t>Issued By</t>
+  </si>
+  <si>
+    <t>GI Line Key (Helper)</t>
+  </si>
+  <si>
+    <t>GI-2026-0001</t>
+  </si>
+  <si>
+    <t>GI-2026-0002</t>
+  </si>
+  <si>
+    <t>Urgent maintenance request completed</t>
+  </si>
+  <si>
+    <t>GI-2026-0003</t>
+  </si>
+  <si>
+    <t>GI-2026-0004</t>
+  </si>
+  <si>
+    <t>5 pcs reserved for quality verification before assembly</t>
+  </si>
+  <si>
+    <t>GI-2026-0005</t>
+  </si>
+  <si>
+    <t>GI-2026-0006</t>
+  </si>
+  <si>
+    <t>GI-2026-0007</t>
+  </si>
+  <si>
+    <t>GI-2026-0008</t>
+  </si>
+  <si>
+    <t>GI-2026-0009</t>
+  </si>
+  <si>
+    <t>GI-2026-0010</t>
   </si>
 </sst>
 </file>
@@ -1012,13 +1321,13 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\)"/>
-    <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\)"/>
-    <numFmt numFmtId="170" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="165" formatCode="0.0%;\(0.0%\)"/>
+    <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
+    <numFmt numFmtId="167" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1111,8 +1420,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1143,8 +1459,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7C80"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1167,12 +1495,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1206,7 +1543,7 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1230,7 +1567,7 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1245,7 +1582,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1261,16 +1598,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1324,10 +1661,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1337,10 +1674,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1355,7 +1692,7 @@
     <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1363,9 +1700,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -1378,12 +1712,210 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="97">
+  <dxfs count="148">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <i/>
+        <color rgb="FF808080"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <i/>
+        <color rgb="FF808080"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1741,6 +2273,672 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF7F7F7F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -2086,7 +3284,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="172" formatCode="yyyy/mm/dd"/>
+      <numFmt numFmtId="169" formatCode="yyyy/mm/dd"/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2122,7 +3320,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\)"/>
+      <numFmt numFmtId="165" formatCode="0.0%;\(0.0%\)"/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2142,7 +3340,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\)"/>
+      <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
@@ -2695,7 +3893,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -2707,7 +3905,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border outline="0">
         <left style="thin">
@@ -2726,7 +3924,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;_-;_-@_-"/>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border outline="0">
         <right style="thin">
@@ -2875,7 +4073,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="170" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="167" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -3031,24 +4229,417 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="01_Master_Material"/>
+      <sheetName val="02_Master_Supplier"/>
+      <sheetName val="03_Master_Location"/>
+      <sheetName val="04_Purchase_Order"/>
+      <sheetName val="05_Goods_Receipt"/>
+      <sheetName val="06_Put_Away"/>
+      <sheetName val="07_Material_Request"/>
+      <sheetName val="08_Picking_List"/>
+      <sheetName val="09_Goods_Issue"/>
+      <sheetName val="10_Stock_Card"/>
+      <sheetName val="11_Cycle_Count"/>
+      <sheetName val="12_Dashboard"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5">
+        <row r="3">
+          <cell r="F3" t="str">
+            <v>GR Line</v>
+          </cell>
+          <cell r="I3" t="str">
+            <v>Material Description</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="F4">
+            <v>10</v>
+          </cell>
+          <cell r="I4" t="str">
+            <v>Engine Oil Filter (Cat 320D)</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="F5">
+            <v>20</v>
+          </cell>
+          <cell r="I5" t="str">
+            <v>Air Filter Element - Primary</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6">
+            <v>10</v>
+          </cell>
+          <cell r="I6" t="str">
+            <v>Hydraulic Cylinder Seal Kit 80mm</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="F7">
+            <v>20</v>
+          </cell>
+          <cell r="I7" t="str">
+            <v>Hydraulic Hose 1/2in x 3m</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="F8">
+            <v>30</v>
+          </cell>
+          <cell r="I8" t="str">
+            <v>Bearing 6205-2RS</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="F9">
+            <v>10</v>
+          </cell>
+          <cell r="I9" t="str">
+            <v>Grease Cartridge NLGI2 400g</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="F10">
+            <v>20</v>
+          </cell>
+          <cell r="I10" t="str">
+            <v>Radiator Coolant 20L</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="F11">
+            <v>10</v>
+          </cell>
+          <cell r="I11" t="str">
+            <v>Flat Washer M12 Zinc Plated</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="F12">
+            <v>10</v>
+          </cell>
+          <cell r="I12" t="str">
+            <v>Industrial Degreaser 20L</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="F13">
+            <v>20</v>
+          </cell>
+          <cell r="I13" t="str">
+            <v>Cabin Air Filter</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="F14">
+            <v>10</v>
+          </cell>
+          <cell r="I14" t="str">
+            <v>Welding Electrode E7018 3.2mm</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="F15">
+            <v>10</v>
+          </cell>
+          <cell r="I15" t="str">
+            <v>Steel Plate 10mm x 2m x 1m</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="F16">
+            <v>20</v>
+          </cell>
+          <cell r="I16" t="str">
+            <v>Hex Bolt M12x50 Grade 8.8</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="F17">
+            <v>10</v>
+          </cell>
+          <cell r="I17" t="str">
+            <v>Steel I-Beam 6m Length</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="F30" t="str">
+            <v>Put Away Qty</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="F31">
+            <v>40</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="F32">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="F33">
+            <v>40</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="F34">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="F35">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="F36">
+            <v>150</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="F37">
+            <v>80</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="F38">
+            <v>5000</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="F39">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="F40">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="F41">
+            <v>250</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="F42">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="F43">
+            <v>2500</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="F44">
+            <v>10</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
+        <row r="3">
+          <cell r="J3" t="str">
+            <v>Material Description</v>
+          </cell>
+          <cell r="P3" t="str">
+            <v>Issue Variance</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4" t="str">
+            <v>Hydraulic Cylinder Seal Kit 80mm</v>
+          </cell>
+          <cell r="P4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5" t="str">
+            <v>Hydraulic Hose 1/2in x 3m</v>
+          </cell>
+          <cell r="P5">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6" t="str">
+            <v>Engine Oil Filter (Cat 320D)</v>
+          </cell>
+          <cell r="P6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7" t="str">
+            <v>Hex Bolt M12x50 Grade 8.8</v>
+          </cell>
+          <cell r="P7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="J8" t="str">
+            <v>Welding Electrode E7018 3.2mm</v>
+          </cell>
+          <cell r="P8">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="J9" t="str">
+            <v>Flat Washer M12 Zinc Plated</v>
+          </cell>
+          <cell r="P9">
+            <v>-5</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="J10" t="str">
+            <v>Steel Plate 10mm x 2m x 1m</v>
+          </cell>
+          <cell r="P10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="J11" t="str">
+            <v>Air Filter Element - Primary</v>
+          </cell>
+          <cell r="P11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="J12" t="str">
+            <v>Track Roller Assembly</v>
+          </cell>
+          <cell r="P12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="J13" t="str">
+            <v>Bucket Teeth (CAT style)</v>
+          </cell>
+          <cell r="P13">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="J14" t="str">
+            <v>Radiator Coolant 20L</v>
+          </cell>
+          <cell r="P14">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="J15" t="str">
+            <v>Turbocharger Assembly (Cat C15)</v>
+          </cell>
+          <cell r="P15">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tbl_MasterMaterial" displayName="tbl_MasterMaterial" ref="A3:N23" totalsRowShown="0">
   <autoFilter ref="A3:N23" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Material Code" dataDxfId="96"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Material Description" dataDxfId="95"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Material Group" dataDxfId="94"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Material Code" dataDxfId="147"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Material Description" dataDxfId="146"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Material Group" dataDxfId="145"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Base UoM"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Primary Supplier Code"/>
-    <tableColumn id="24" xr3:uid="{0F116849-4911-4B80-B390-3C1C1D0A9D49}" name="Default Storage Location" dataDxfId="93"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Standard Cost (per Base UoM)" dataDxfId="92"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Criticality Flag" dataDxfId="91"/>
+    <tableColumn id="24" xr3:uid="{0F116849-4911-4B80-B390-3C1C1D0A9D49}" name="Default Storage Location" dataDxfId="144"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Standard Cost (per Base UoM)" dataDxfId="143"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Criticality Flag" dataDxfId="142"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Storage/Handling Class"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Min Stock Level"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Max Stock Level"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Lead Time (Days)"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Status"/>
-    <tableColumn id="22" xr3:uid="{BC7C3BEF-CB66-4A5F-9E71-E29F8E60C070}" name="Remarks" dataDxfId="90"/>
+    <tableColumn id="22" xr3:uid="{BC7C3BEF-CB66-4A5F-9E71-E29F8E60C070}" name="Remarks" dataDxfId="141"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{25FBEA94-EC69-47A8-A8B4-103E138DBD45}" name="tbl_GoodsIssue" displayName="tbl_GoodsIssue" ref="A3:U15" totalsRowShown="0">
+  <autoFilter ref="A3:U15" xr:uid="{25FBEA94-EC69-47A8-A8B4-103E138DBD45}"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{6B1B12C1-F256-427A-9E2F-323ECF75748C}" name="GI Number"/>
+    <tableColumn id="2" xr3:uid="{2DF9802A-C24B-435F-AD47-4698F37FE200}" name="GI Line"/>
+    <tableColumn id="3" xr3:uid="{A3C22BB4-F821-4457-AA07-C417AC098CD2}" name="GI Date"/>
+    <tableColumn id="4" xr3:uid="{1A884DF3-8DD6-4CE9-93ED-FA1CB04768F6}" name="Pick Number"/>
+    <tableColumn id="5" xr3:uid="{1AE482A6-8412-46CE-990F-E37FE1550930}" name="Pick Line"/>
+    <tableColumn id="19" xr3:uid="{AC18BD1A-085F-4822-864F-A36AEAF3187C}" name="Request Number" dataDxfId="67">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="20" xr3:uid="{1E49D15C-220B-47AC-9CA9-6C519D209D42}" name="Request Line" dataDxfId="66">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{41CB3683-6C31-4CDA-8F57-6517C3E41E0A}" name="Pick Line Key (Helper)" dataDxfId="65">
+      <calculatedColumnFormula>D4&amp;"-"&amp;E4</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{106ED3C1-CAAF-4A07-91B8-C6EF79F2D2FB}" name="Material Code">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{6194A028-A5FC-4B2F-916D-0487C09EEAB0}" name="Material Description">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{F6C00B0D-7BF1-4516-947E-950BBBC4AC44}" name="Base UoM" dataDxfId="64">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{FDE08550-5A0D-4B45-B0EB-39A3F7F5327B}" name="Issuing Location (Ref)" dataDxfId="63">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{EFC2147A-68C4-40E7-AC1F-291B5BF6E01C}" name="Requesting Department (Ref)" dataDxfId="62">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{241BCCED-8CE2-45C0-B5A0-EB281804E5C9}" name="Quantity Picked (Ref)" dataDxfId="61">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{7E65839F-364E-4284-AF93-048039A11EF2}" name="Quantity Issued"/>
+    <tableColumn id="14" xr3:uid="{378E0A83-0410-4F9D-B513-F95B77F93BB3}" name="Issue Variance" dataDxfId="60">
+      <calculatedColumnFormula>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{AB614138-7B13-4C46-943F-774255F936E4}" name="Issue Status" dataDxfId="59">
+      <calculatedColumnFormula>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="21" xr3:uid="{82454FE2-C266-4763-B459-4018C5D9D8B8}" name="Issued By" dataDxfId="58"/>
+    <tableColumn id="22" xr3:uid="{4C97B95A-D48D-4A89-8F03-4F95F8CEE7D8}" name="Received By" dataDxfId="57"/>
+    <tableColumn id="16" xr3:uid="{9AB5B34E-9130-4977-9CE4-70C3B46EB23D}" name="Remarks" dataDxfId="56"/>
+    <tableColumn id="17" xr3:uid="{3D68FD7A-D251-490A-9730-4A0D6FA0FFD7}" name="GI Line Key (Helper)">
+      <calculatedColumnFormula>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3095,7 +4686,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Location Code"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Location Description"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Zone"/>
-    <tableColumn id="8" xr3:uid="{276A2345-C837-4FC6-B4E0-FF35EB523268}" name="Location Type" dataDxfId="89"/>
+    <tableColumn id="8" xr3:uid="{276A2345-C837-4FC6-B4E0-FF35EB523268}" name="Location Type" dataDxfId="140"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Storage/Handling Requirement"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Pickable Flag"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Capacity (Max Qty)"/>
@@ -3116,37 +4707,37 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="PO Line"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="PO Date"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Supplier Code"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Supplier Name" dataDxfId="88">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Supplier Name" dataDxfId="139">
       <calculatedColumnFormula>VLOOKUP(tbl_PurchaseOrder[[#This Row],[Supplier Code]],tbl_MasterSupplier[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Material Code"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Material Description" dataDxfId="87">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Material Description" dataDxfId="138">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PurchaseOrder[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Purchase UoM" dataDxfId="86"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Ordered Qty" dataDxfId="85" totalsRowDxfId="84"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Unit Price" dataDxfId="83" totalsRowDxfId="82"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Line Total" dataDxfId="81" totalsRowDxfId="80">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Purchase UoM" dataDxfId="137"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Ordered Qty" dataDxfId="136" totalsRowDxfId="135"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Unit Price" dataDxfId="134" totalsRowDxfId="133"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Line Total" dataDxfId="132" totalsRowDxfId="131">
       <calculatedColumnFormula>tbl_PurchaseOrder[[#This Row],[Ordered Qty]]*J4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="Order Priority" dataDxfId="79" totalsRowDxfId="78"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="Order Priority" dataDxfId="130" totalsRowDxfId="129"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="Lead Time (Days)">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PurchaseOrder[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Lead Time (Days)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="Expected Delivery Date" dataDxfId="77">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="Expected Delivery Date" dataDxfId="128">
       <calculatedColumnFormula>tbl_PurchaseOrder[[#This Row],[PO Date]]+tbl_PurchaseOrder[[#This Row],[Lead Time (Days)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{09E53041-1B48-4B81-BCF8-287332AE53AE}" name="Received Qty" dataDxfId="76" totalsRowDxfId="75">
+    <tableColumn id="13" xr3:uid="{09E53041-1B48-4B81-BCF8-287332AE53AE}" name="Received Qty" dataDxfId="127" totalsRowDxfId="126">
       <calculatedColumnFormula>SUMIFS(tbl_GoodsReceipt[Received Qty],tbl_GoodsReceipt[PO Line Key (Helper)],tbl_PurchaseOrder[[#This Row],[PO Line Key (Helper)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{123695AE-1CB2-4070-BEE2-29FE092ACFA7}" name="Outstanding Qty" dataDxfId="74" totalsRowDxfId="73">
+    <tableColumn id="14" xr3:uid="{123695AE-1CB2-4070-BEE2-29FE092ACFA7}" name="Outstanding Qty" dataDxfId="125" totalsRowDxfId="124">
       <calculatedColumnFormula>IFERROR(tbl_PurchaseOrder[[#This Row],[Received Qty]]-tbl_PurchaseOrder[[#This Row],[Ordered Qty]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="PO Status" dataDxfId="72">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="PO Status" dataDxfId="123">
       <calculatedColumnFormula>IF(tbl_PurchaseOrder[[#This Row],[Received Qty]]=0,"Open",IF(tbl_PurchaseOrder[[#This Row],[Received Qty]]&lt;tbl_PurchaseOrder[[#This Row],[Ordered Qty]],"Partial", "Closed"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Remarks" dataDxfId="71"/>
-    <tableColumn id="19" xr3:uid="{195CE6D1-9D3F-4D81-9DE2-B82EEBF35742}" name="PO Line Key (Helper)" dataDxfId="70" totalsRowDxfId="69">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Remarks" dataDxfId="122"/>
+    <tableColumn id="19" xr3:uid="{195CE6D1-9D3F-4D81-9DE2-B82EEBF35742}" name="PO Line Key (Helper)" dataDxfId="121" totalsRowDxfId="120">
       <calculatedColumnFormula>tbl_PurchaseOrder[[#This Row],[PO Number]]&amp;"-"&amp;tbl_PurchaseOrder[[#This Row],[PO Line]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3165,52 +4756,52 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="GR Line"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="GR Date"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="PO Number"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="PO Line" dataDxfId="68"/>
-    <tableColumn id="29" xr3:uid="{32467FAF-3D7D-4CA5-9707-3FB4E795D1FA}" name="PO Line Key (Helper)" dataDxfId="67">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="PO Line" dataDxfId="119"/>
+    <tableColumn id="29" xr3:uid="{32467FAF-3D7D-4CA5-9707-3FB4E795D1FA}" name="PO Line Key (Helper)" dataDxfId="118">
       <calculatedColumnFormula>tbl_GoodsReceipt[[#This Row],[PO Number]]&amp;"-"&amp;tbl_GoodsReceipt[[#This Row],[PO Line]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E8DA1EE4-E020-4801-93F4-A35A7E1B2656}" name="Supplier Code" dataDxfId="66">
+    <tableColumn id="6" xr3:uid="{E8DA1EE4-E020-4801-93F4-A35A7E1B2656}" name="Supplier Code" dataDxfId="117">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Supplier Code])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Supplier Name" dataDxfId="65">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Supplier Name" dataDxfId="116">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[Supplier Code]],tbl_MasterSupplier[Supplier Code],tbl_MasterSupplier[Supplier Name])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Material Code" dataDxfId="64">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Material Code" dataDxfId="115">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Material Code])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Material Description" dataDxfId="63">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Material Description" dataDxfId="114">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="Order Qty" dataDxfId="62">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="Order Qty" dataDxfId="113">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Ordered Qty])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="Purchase UoM" dataDxfId="61">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="Purchase UoM" dataDxfId="112">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Purchase UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="Unit Price" dataDxfId="60">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="Unit Price" dataDxfId="111">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Unit Price])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" name="Expected Delivery Date" dataDxfId="59">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" name="Expected Delivery Date" dataDxfId="110">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Expected Delivery Date])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{76F9E9A1-1F34-4FAD-9BFD-02A48B886435}" name="Delivery Note No." dataDxfId="58"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" name="Receiving Dock" dataDxfId="57"/>
-    <tableColumn id="27" xr3:uid="{C970C051-0950-4A04-BC06-F42CE88CB783}" name="Received By" dataDxfId="56"/>
+    <tableColumn id="21" xr3:uid="{76F9E9A1-1F34-4FAD-9BFD-02A48B886435}" name="Delivery Note No." dataDxfId="109"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" name="Receiving Dock" dataDxfId="108"/>
+    <tableColumn id="27" xr3:uid="{C970C051-0950-4A04-BC06-F42CE88CB783}" name="Received By" dataDxfId="107"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="Received Qty"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" name="Accepted Qty"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" name="Rejected Qty" dataDxfId="55">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" name="Rejected Qty" dataDxfId="106">
       <calculatedColumnFormula>tbl_GoodsReceipt[[#This Row],[Received Qty]]-tbl_GoodsReceipt[[#This Row],[Accepted Qty]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" name="Inspection Result"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0400-000011000000}" name="Rejection Reason"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" name="Batch/Lot Number"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0400-000016000000}" name="Received Variance" dataDxfId="54">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0400-000016000000}" name="Received Variance" dataDxfId="105">
       <calculatedColumnFormula>tbl_GoodsReceipt[[#This Row],[Received Qty]]-tbl_GoodsReceipt[[#This Row],[Order Qty]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0400-000017000000}" name="Received Variance %">
       <calculatedColumnFormula>IFERROR(tbl_GoodsReceipt[[#This Row],[Received Variance]]/tbl_GoodsReceipt[[#This Row],[Order Qty]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{9903FC18-7740-482D-9ABE-94B8CD52CA29}" name="Delivery Status" dataDxfId="53">
+    <tableColumn id="28" xr3:uid="{9903FC18-7740-482D-9ABE-94B8CD52CA29}" name="Delivery Status" dataDxfId="104">
       <calculatedColumnFormula>IF(tbl_GoodsReceipt[[#This Row],[GR Date]]&lt;=tbl_GoodsReceipt[[#This Row],[Expected Delivery Date]],"On-time","Late")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" name="Put-Away Status"/>
@@ -3224,59 +4815,144 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="tbl_PutAway" displayName="tbl_PutAway" ref="A3:W17" totalsRowShown="0">
-  <autoFilter ref="A3:W17" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6B3DB970-7D09-43A7-A358-6B1F939A14BC}" name="tbl_PutAway2" displayName="tbl_PutAway2" ref="A3:W17" totalsRowShown="0">
+  <autoFilter ref="A3:W17" xr:uid="{6B3DB970-7D09-43A7-A358-6B1F939A14BC}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Put Away Number"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Put Away Line"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Put Away Date"/>
-    <tableColumn id="9" xr3:uid="{3D1409EE-9BE5-4C77-8E8C-75FBB533A1BA}" name="GR Date" dataDxfId="52">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{B2820B32-D7DD-46E0-8DC9-85D6D0F2F498}" name="Put Away Number"/>
+    <tableColumn id="2" xr3:uid="{0F13D28A-BA08-441F-BEC4-7D6037733212}" name="Put Away Line"/>
+    <tableColumn id="3" xr3:uid="{F64021F0-B759-425B-A31C-41586E8E37C9}" name="Put Away Date"/>
+    <tableColumn id="9" xr3:uid="{E03F1EBB-6C5E-4F01-BF63-B997B72A75B5}" name="GR Date" dataDxfId="103">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="GR Number"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="GR Line" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="GR Line Key (Helper)" dataDxfId="50">
-      <calculatedColumnFormula>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</calculatedColumnFormula>
+    <tableColumn id="4" xr3:uid="{9CD70814-3501-46D0-ADC4-95B460051A76}" name="GR Number"/>
+    <tableColumn id="5" xr3:uid="{AD89AACB-2035-4547-815B-97B54A79F58B}" name="GR Line" dataDxfId="102"/>
+    <tableColumn id="6" xr3:uid="{E922F599-6AE7-4A51-8543-1683E90BDD71}" name="GR Line Key (Helper)" dataDxfId="101">
+      <calculatedColumnFormula>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Material Code">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</calculatedColumnFormula>
+    <tableColumn id="7" xr3:uid="{0CF55A9E-39F1-4F68-9223-C7DD92AD7F96}" name="Material Code">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Material Description" dataDxfId="49">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</calculatedColumnFormula>
+    <tableColumn id="8" xr3:uid="{4950093A-EBB0-45E7-9BC7-DF3E9210FC3D}" name="Material Description" dataDxfId="100">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{17CC66FF-3B10-4724-A531-9ABD3C5CB8D1}" name="Batch/Lot Number" dataDxfId="48">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</calculatedColumnFormula>
+    <tableColumn id="23" xr3:uid="{59D088FB-A71A-4C0D-8683-EAAED5821813}" name="Batch/Lot Number" dataDxfId="99">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="Accepted Qty">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</calculatedColumnFormula>
+    <tableColumn id="12" xr3:uid="{7146D458-8B1D-4A49-9C94-4D7E7D5331F0}" name="Accepted Qty">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{28CCFCA5-F3BC-430A-80E6-5C20D5AAAE8F}" name="Purchase UoM" dataDxfId="47">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</calculatedColumnFormula>
+    <tableColumn id="17" xr3:uid="{50508DE8-DD5C-441D-B90B-E0180BBE214C}" name="Purchase UoM" dataDxfId="98">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{0A641E53-0249-44B9-9E19-52E853A7C026}" name="Put Away Qty" dataDxfId="46"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="Base UoM" dataDxfId="45">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</calculatedColumnFormula>
+    <tableColumn id="16" xr3:uid="{8C2E0FD8-30A9-4858-A91C-82CE5FDFB7BE}" name="Put Away Qty" dataDxfId="97"/>
+    <tableColumn id="13" xr3:uid="{EAED5A2E-494D-473B-BCB6-38C1D65067E2}" name="Base UoM" dataDxfId="96">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="From Location" dataDxfId="44">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</calculatedColumnFormula>
+    <tableColumn id="15" xr3:uid="{73D252CF-0430-42B8-B496-F40210DCD95F}" name="From Location" dataDxfId="95">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E1EA826-7DDD-4C65-AB2E-9676F8A827A7}" name="Suggested Storage Location (Ref)" dataDxfId="43">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{8AEDE3C9-538E-49FC-8D4C-919E5B784887}" name="Suggested Storage Location (Ref)" dataDxfId="94">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="Storage/Handling Class" dataDxfId="42">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</calculatedColumnFormula>
+    <tableColumn id="14" xr3:uid="{AFA3AA67-87FC-4898-B051-166FA534C265}" name="Storage/Handling Class" dataDxfId="93">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{BB70C6C7-B755-4415-A577-FB1FBECE67FD}" name="To Location" dataDxfId="41"/>
-    <tableColumn id="19" xr3:uid="{1445C40B-D3A5-4C1B-9654-FF2E02CAEB6A}" name="Location Storage/Handling Requirement" dataDxfId="40">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</calculatedColumnFormula>
+    <tableColumn id="24" xr3:uid="{A7430B9B-8A0B-4B52-BC84-AA7AF710FD0B}" name="To Location" dataDxfId="92"/>
+    <tableColumn id="19" xr3:uid="{AA2AFBDA-DFE9-4C45-B3A7-491FCE86E01B}" name="Location Storage/Handling Requirement" dataDxfId="91">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{47D4BE73-8080-42B6-985B-6CB165C06B54}" name="Location Match Check" dataDxfId="39">
-      <calculatedColumnFormula>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</calculatedColumnFormula>
+    <tableColumn id="20" xr3:uid="{4843B501-914D-43BE-A090-204AD9839622}" name="Location Match Check" dataDxfId="90">
+      <calculatedColumnFormula>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0500-000012000000}" name="Put Away Status" dataDxfId="38"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0500-000015000000}" name="Remarks"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0500-000016000000}" name="Put-Away Line Key (Helper)">
-      <calculatedColumnFormula>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</calculatedColumnFormula>
+    <tableColumn id="18" xr3:uid="{5359C52F-3F31-4E3F-8C3E-0329EC18658B}" name="Put Away Status" dataDxfId="89">
+      <calculatedColumnFormula>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="21" xr3:uid="{5B61C99F-3F68-4280-9CB7-4C8E8D62C9A3}" name="Remarks"/>
+    <tableColumn id="22" xr3:uid="{A77B1BD7-E90D-465A-8F3C-97010DD6AC5D}" name="Put-Away Line Key (Helper)">
+      <calculatedColumnFormula>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7729DF7E-C144-4719-998B-52088A29B668}" name="tbl_MaterialRequest" displayName="tbl_MaterialRequest" ref="A3:R18" totalsRowShown="0">
+  <autoFilter ref="A3:R18" xr:uid="{7729DF7E-C144-4719-998B-52088A29B668}"/>
+  <tableColumns count="18">
+    <tableColumn id="20" xr3:uid="{3C0390E3-68A0-4909-B67E-E5F8021AE8E9}" name="Request Number" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{8A70104B-655A-4746-9E1F-F9D831EC827B}" name="Request Line" dataDxfId="87"/>
+    <tableColumn id="3" xr3:uid="{7A1A07AB-F1A4-430C-81EA-CCED420351ED}" name="Request Date"/>
+    <tableColumn id="10" xr3:uid="{8CF7B51D-F45D-465F-BA3A-9BD7A73286FE}" name="Required Date" dataDxfId="86"/>
+    <tableColumn id="4" xr3:uid="{106B013D-6E3E-4877-AA7B-7A7178DEBDF7}" name="Requesting Department"/>
+    <tableColumn id="11" xr3:uid="{F1E8D945-6C57-48DC-ABC4-A51DD1B9F107}" name="Requester" dataDxfId="85"/>
+    <tableColumn id="5" xr3:uid="{8F80EC92-5E02-40E0-8FBC-ECE6EEA27E27}" name="Material Code"/>
+    <tableColumn id="6" xr3:uid="{A432A144-E238-4378-885F-6A2B166171B6}" name="Material Description">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{7C242AD8-8411-4074-8E37-FE98BBDD159A}" name="Base UoM">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{670A38B4-8F71-49A1-BDF8-E9F5A443B6AD}" name="Quantity Requested"/>
+    <tableColumn id="9" xr3:uid="{6CBB2C3C-4968-4DFC-B36B-E8F03DAE700A}" name="Request Priority"/>
+    <tableColumn id="13" xr3:uid="{B8F6A0CE-1188-44C5-B4A1-4C8553A8221E}" name="Available Stock (Ref)" dataDxfId="84"/>
+    <tableColumn id="14" xr3:uid="{B6975D28-9349-45DC-8455-FA1FBF6F3D6A}" name="Stock Sufficiency Check" dataDxfId="83">
+      <calculatedColumnFormula>IF(L4&gt;=J4,"Sufficient","Insufficient - Review")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="18" xr3:uid="{3EF748E6-D130-4232-8709-91DFD88B6DCC}" name="Approval Status" dataDxfId="82"/>
+    <tableColumn id="12" xr3:uid="{CA251D90-C7FB-4D0C-AE6E-F5D1C7F4B373}" name="Total Issued (Ref)" dataDxfId="81"/>
+    <tableColumn id="15" xr3:uid="{A3F09887-B081-42F6-9576-4ACFBC6E3BF5}" name="Request Status" dataDxfId="80"/>
+    <tableColumn id="16" xr3:uid="{16004DC1-4424-48C2-9110-5E4DB91701DB}" name="Remarks" dataDxfId="79"/>
+    <tableColumn id="17" xr3:uid="{65C60F4B-8165-4E50-97C2-9A71F557F348}" name="Request Line Key (Helper)">
+      <calculatedColumnFormula>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{65A51F98-DAEB-4D43-BD4D-591A695CDF69}" name="tbl_PickingList11" displayName="tbl_PickingList11" ref="A3:S15" totalsRowShown="0">
+  <autoFilter ref="A3:S15" xr:uid="{65A51F98-DAEB-4D43-BD4D-591A695CDF69}"/>
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{632F096F-0163-45F3-B4F2-65A87147D80A}" name="Pick Number"/>
+    <tableColumn id="2" xr3:uid="{2C07203A-D801-48CC-807F-C27B85CCB303}" name="Pick Line"/>
+    <tableColumn id="3" xr3:uid="{40E4E0BB-54BC-45B6-9EFB-267069E0F946}" name="Pick Date"/>
+    <tableColumn id="4" xr3:uid="{B21BCC45-6F55-4BA2-B10A-F85D1150EB9C}" name="Request Number"/>
+    <tableColumn id="5" xr3:uid="{C6F5BB68-561B-4485-A2CD-AD53C44ADAEE}" name="Request Line"/>
+    <tableColumn id="6" xr3:uid="{8C3B4260-BBF6-4AEF-846E-0EEDE6345047}" name="Request Line Key (Helper)">
+      <calculatedColumnFormula>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{83FF2341-6753-401A-BD35-82FBC54F8919}" name="Material Code" dataDxfId="78">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{95F92AD2-7BD7-48DA-A284-BD9DDAFA22A0}" name="Material Description" dataDxfId="77">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="21" xr3:uid="{48BBAD60-5074-455D-A78B-41945458B773}" name="Base UoM" dataDxfId="76">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{9B47A178-786C-4D2B-A4E3-26FFCB44BFE5}" name="Requesting Department (Ref)" dataDxfId="75">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{642C0F18-9253-4A46-ACEB-8FE96D94AE20}" name="Request Priority (Ref)" dataDxfId="74">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{99E8E712-2A10-4694-AC2D-BD8432BA94FF}" name="Quantity Requested (Ref)" dataDxfId="73">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{24F438EE-14EA-42DC-BE5F-E654E9C1A89F}" name="Pick Location (Ref)" dataDxfId="72">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Material Code]],[1]!tbl_PutAway[Material Code],[1]!tbl_PutAway[To Location])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{CCFD5510-86EE-4EDE-A614-E8FDD6BF4E60}" name="Available Stock" dataDxfId="71"/>
+    <tableColumn id="16" xr3:uid="{06C34751-72A9-4F60-97A9-C168A378B797}" name="Quantity Picked" dataDxfId="70"/>
+    <tableColumn id="17" xr3:uid="{7C7B497B-9F75-4CED-972B-4AF509AF2098}" name="Pick Status" dataDxfId="69">
+      <calculatedColumnFormula>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="25" xr3:uid="{0E9ACBD8-03BA-4C05-B55B-39E3F066B4B5}" name="Picker" dataDxfId="68"/>
+    <tableColumn id="19" xr3:uid="{FC95FDE1-1294-4F68-8595-7AADEDAB4AFF}" name="Remarks"/>
+    <tableColumn id="20" xr3:uid="{97D2004D-40DB-4252-B0F6-DC6234F5B8FB}" name="Pick Line Key (Helper)">
+      <calculatedColumnFormula>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3478,22 +5154,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
     </row>
     <row r="3" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -4385,85 +6061,85 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="68"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
+      <c r="A27" s="67"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="68"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
+      <c r="A28" s="67"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="68"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="69"/>
+      <c r="A29" s="67"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="68"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
+      <c r="A30" s="67"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="68"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="68"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
+      <c r="A31" s="67"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="68"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="69"/>
-      <c r="B32" s="69"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
+      <c r="A32" s="68"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="68"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="68"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="23"/>
       <c r="B34" s="23"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="69"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="68"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="23"/>
       <c r="B35" s="23"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="23"/>
@@ -4562,26 +6238,26 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A4:N23">
-    <cfRule type="expression" dxfId="37" priority="26">
+    <cfRule type="expression" dxfId="55" priority="26">
       <formula>$M4="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="27">
+    <cfRule type="expression" dxfId="54" priority="27">
       <formula>$H4="Critical Spare"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24:N32 A54:N500 I53:N53 A53:D53">
-    <cfRule type="expression" dxfId="35" priority="18">
+  <conditionalFormatting sqref="A24:N32 A53:D53 I53:N53 A54:N500">
+    <cfRule type="expression" dxfId="53" priority="18">
       <formula>$N24="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="19">
+    <cfRule type="expression" dxfId="52" priority="19">
       <formula>$H24="Critical Spare"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:I52">
-    <cfRule type="expression" dxfId="33" priority="77">
+    <cfRule type="expression" dxfId="51" priority="77">
       <formula>$I33="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="78">
+    <cfRule type="expression" dxfId="50" priority="78">
       <formula>$C33="Critical Spare"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4687,17 +6363,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
     </row>
     <row r="3" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -5072,60 +6748,60 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="68"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
+      <c r="A17" s="67"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="68"/>
-      <c r="B18" s="69"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="68"/>
-      <c r="B19" s="69"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="68"/>
-      <c r="B20" s="69"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="68"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="69"/>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
+      <c r="A22" s="68"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="69"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
+      <c r="A23" s="68"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="70"/>
-      <c r="B24" s="70"/>
-      <c r="C24" s="70"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
+      <c r="A24" s="69"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
@@ -5236,23 +6912,23 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A4:I13">
-    <cfRule type="expression" dxfId="31" priority="37">
+    <cfRule type="expression" dxfId="49" priority="37">
       <formula>$I4="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="38">
+    <cfRule type="expression" dxfId="48" priority="38">
       <formula>$H4="Preferred"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H23">
-    <cfRule type="expression" dxfId="29" priority="7">
+    <cfRule type="expression" dxfId="47" priority="7">
       <formula>$H14="Under Review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:Q13">
-    <cfRule type="expression" dxfId="28" priority="2">
+    <cfRule type="expression" dxfId="46" priority="2">
       <formula>$Q5="aktif"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="3">
+    <cfRule type="expression" dxfId="45" priority="3">
       <formula>$Q5="tidak aktif"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5303,16 +6979,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
     </row>
     <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -5993,28 +7669,28 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A28:G36 A61:G513">
-    <cfRule type="expression" dxfId="26" priority="2">
+    <cfRule type="expression" dxfId="44" priority="2">
       <formula>$G28="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="3">
+    <cfRule type="expression" dxfId="43" priority="3">
       <formula>$D28="Hazardous"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:H27">
-    <cfRule type="expression" dxfId="24" priority="41">
+    <cfRule type="expression" dxfId="42" priority="41">
       <formula>$H4="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="42">
+    <cfRule type="expression" dxfId="41" priority="42">
       <formula>$E4="Hazardous"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E36 E61:E513">
-    <cfRule type="expression" dxfId="22" priority="4">
+    <cfRule type="expression" dxfId="40" priority="4">
       <formula>$E28="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F27">
-    <cfRule type="expression" dxfId="21" priority="46">
+    <cfRule type="expression" dxfId="39" priority="46">
       <formula>$F4="No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6076,27 +7752,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="80"/>
     </row>
     <row r="3" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -7538,76 +9214,76 @@
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="68"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
+      <c r="A29" s="67"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="68"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
+      <c r="A30" s="67"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="68"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="68"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
+      <c r="A31" s="67"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="68"/>
-      <c r="B32" s="69"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
+      <c r="A32" s="67"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="68"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
+      <c r="A33" s="67"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="68"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="68"/>
-      <c r="B34" s="69"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
+      <c r="A34" s="67"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="68"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="68"/>
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
+      <c r="A35" s="67"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="69"/>
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
+      <c r="A36" s="68"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="68"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="69"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="69"/>
+      <c r="A37" s="68"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="68"/>
     </row>
     <row r="40" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22"/>
@@ -7846,37 +9522,37 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="L4:L25">
-    <cfRule type="expression" dxfId="20" priority="56">
+    <cfRule type="expression" dxfId="38" priority="56">
       <formula>$L4="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26:N511">
-    <cfRule type="expression" dxfId="19" priority="3">
+    <cfRule type="expression" dxfId="37" priority="3">
       <formula>$N26="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q25">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>$Q4="Partial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="64">
+    <cfRule type="expression" dxfId="35" priority="64">
       <formula>$Q4="Cancelled"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="65">
+    <cfRule type="expression" dxfId="34" priority="65">
       <formula>$Q4="Closed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="66">
+    <cfRule type="expression" dxfId="33" priority="66">
       <formula>$Q4="Open"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R26:R511">
-    <cfRule type="expression" dxfId="14" priority="4">
+    <cfRule type="expression" dxfId="32" priority="4">
       <formula>$R26="Cancelled"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="5">
+    <cfRule type="expression" dxfId="31" priority="5">
       <formula>$R26="Closed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="6">
+    <cfRule type="expression" dxfId="30" priority="6">
       <formula>$R26="Open"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7958,37 +9634,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="80" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="80"/>
+      <c r="T1" s="80"/>
+      <c r="U1" s="80"/>
+      <c r="V1" s="80"/>
+      <c r="W1" s="80"/>
+      <c r="X1" s="80"/>
+      <c r="Y1" s="80"/>
+      <c r="Z1" s="80"/>
+      <c r="AA1" s="80"/>
+      <c r="AB1" s="80"/>
+      <c r="AC1" s="80"/>
     </row>
     <row r="3" spans="1:29" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -9529,105 +11205,105 @@
       <c r="AA20" s="57"/>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A21" s="68"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
       <c r="AA21" s="57"/>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A22" s="68"/>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
+      <c r="A22" s="67"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A23" s="68"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
+      <c r="A23" s="67"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A24" s="68"/>
-      <c r="B24" s="69"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
+      <c r="A24" s="67"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A25" s="68"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
+      <c r="A25" s="67"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A26" s="68"/>
-      <c r="B26" s="69"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
+      <c r="A26" s="67"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A27" s="68"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
+      <c r="A27" s="67"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A28" s="69"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
+      <c r="A28" s="68"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A29" s="69"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="69"/>
-      <c r="H29" s="69"/>
+      <c r="A29" s="68"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A30" s="69"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
+      <c r="A30" s="68"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="68"/>
+      <c r="H30" s="68"/>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="22"/>
@@ -9890,33 +11566,33 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="S19:S509">
-    <cfRule type="expression" dxfId="11" priority="6">
+    <cfRule type="expression" dxfId="29" priority="6">
       <formula>$S19="Fully Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="7">
+    <cfRule type="expression" dxfId="28" priority="7">
       <formula>$S19="Partially Accepted"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4:U18">
-    <cfRule type="expression" dxfId="9" priority="61">
+    <cfRule type="expression" dxfId="27" priority="61">
       <formula>$U4="Fully Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="62">
+    <cfRule type="expression" dxfId="26" priority="62">
       <formula>$U4="Partially Accepted"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X4:X509">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="25" priority="8">
       <formula>$X4&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:Z18">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>$Z4="Late"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA509">
-    <cfRule type="expression" dxfId="5" priority="9">
+    <cfRule type="expression" dxfId="23" priority="9">
       <formula>$AA4="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9997,31 +11673,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
     </row>
     <row r="3" spans="1:23" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -10105,7 +11781,7 @@
         <v>46244</v>
       </c>
       <c r="D4" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46244</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -10115,66 +11791,66 @@
         <v>10</v>
       </c>
       <c r="G4" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0001-10</v>
       </c>
       <c r="H4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00003</v>
       </c>
       <c r="I4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Engine Oil Filter (Cat 320D)</v>
       </c>
       <c r="J4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-FLT-260810</v>
       </c>
       <c r="K4" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>40</v>
       </c>
       <c r="L4" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>PCS</v>
       </c>
       <c r="M4" s="7">
         <v>40</v>
       </c>
       <c r="N4" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>PCS</v>
       </c>
       <c r="O4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-02</v>
       </c>
       <c r="P4" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>A-02-01-01</v>
       </c>
       <c r="Q4" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Standard</v>
       </c>
       <c r="R4" s="6" t="s">
         <v>153</v>
       </c>
       <c r="S4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Standard</v>
       </c>
       <c r="T4" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U4" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V4" s="6"/>
       <c r="W4" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0001-10</v>
       </c>
     </row>
@@ -10189,7 +11865,7 @@
         <v>46244</v>
       </c>
       <c r="D5" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46244</v>
       </c>
       <c r="E5" s="6" t="s">
@@ -10199,66 +11875,66 @@
         <v>20</v>
       </c>
       <c r="G5" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0001-20</v>
       </c>
       <c r="H5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00007</v>
       </c>
       <c r="I5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Air Filter Element - Primary</v>
       </c>
       <c r="J5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-FLT-260810</v>
       </c>
       <c r="K5" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>20</v>
       </c>
       <c r="L5" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>PCS</v>
       </c>
       <c r="M5" s="7">
         <v>20</v>
       </c>
       <c r="N5" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>PCS</v>
       </c>
       <c r="O5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-02</v>
       </c>
       <c r="P5" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>A-02-01-02</v>
       </c>
       <c r="Q5" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Standard</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>157</v>
       </c>
       <c r="S5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Standard</v>
       </c>
       <c r="T5" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U5" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V5" s="6"/>
       <c r="W5" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0001-20</v>
       </c>
     </row>
@@ -10273,7 +11949,7 @@
         <v>46249</v>
       </c>
       <c r="D6" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46249</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -10283,66 +11959,66 @@
         <v>10</v>
       </c>
       <c r="G6" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0002-10</v>
       </c>
       <c r="H6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00001</v>
       </c>
       <c r="I6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Hydraulic Cylinder Seal Kit 80mm</v>
       </c>
       <c r="J6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-HYD-260815</v>
       </c>
       <c r="K6" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>40</v>
       </c>
       <c r="L6" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>PCS</v>
       </c>
       <c r="M6" s="7">
         <v>40</v>
       </c>
       <c r="N6" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>PCS</v>
       </c>
       <c r="O6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-01</v>
       </c>
       <c r="P6" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>A-01-01-01</v>
       </c>
       <c r="Q6" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Standard</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>152</v>
       </c>
       <c r="S6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Standard</v>
       </c>
       <c r="T6" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U6" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V6" s="6"/>
       <c r="W6" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0002-10</v>
       </c>
     </row>
@@ -10357,7 +12033,7 @@
         <v>46249</v>
       </c>
       <c r="D7" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46249</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -10367,66 +12043,66 @@
         <v>20</v>
       </c>
       <c r="G7" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0002-20</v>
       </c>
       <c r="H7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00008</v>
       </c>
       <c r="I7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Hydraulic Hose 1/2in x 3m</v>
       </c>
       <c r="J7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-HYD-260815</v>
       </c>
       <c r="K7" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>20</v>
       </c>
       <c r="L7" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>PCS</v>
       </c>
       <c r="M7" s="7">
         <v>20</v>
       </c>
       <c r="N7" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>PCS</v>
       </c>
       <c r="O7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-01</v>
       </c>
       <c r="P7" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>A-01-02-01</v>
       </c>
       <c r="Q7" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Standard</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>158</v>
       </c>
       <c r="S7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Standard</v>
       </c>
       <c r="T7" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U7" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V7" s="6"/>
       <c r="W7" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0002-20</v>
       </c>
     </row>
@@ -10441,7 +12117,7 @@
         <v>46249</v>
       </c>
       <c r="D8" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46249</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -10451,66 +12127,66 @@
         <v>30</v>
       </c>
       <c r="G8" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0002-30</v>
       </c>
       <c r="H8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00019</v>
       </c>
       <c r="I8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Bearing 6205-2RS</v>
       </c>
       <c r="J8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-BRG-260815</v>
       </c>
       <c r="K8" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>100</v>
       </c>
       <c r="L8" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>PCS</v>
       </c>
       <c r="M8" s="7">
         <v>100</v>
       </c>
       <c r="N8" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>PCS</v>
       </c>
       <c r="O8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-01</v>
       </c>
       <c r="P8" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>A-01-02-02</v>
       </c>
       <c r="Q8" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Standard</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>166</v>
       </c>
       <c r="S8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Standard</v>
       </c>
       <c r="T8" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U8" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V8" s="6"/>
       <c r="W8" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0002-30</v>
       </c>
     </row>
@@ -10525,7 +12201,7 @@
         <v>46249</v>
       </c>
       <c r="D9" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46249</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -10535,66 +12211,66 @@
         <v>10</v>
       </c>
       <c r="G9" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0003-10</v>
       </c>
       <c r="H9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00009</v>
       </c>
       <c r="I9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Grease Cartridge NLGI2 400g</v>
       </c>
       <c r="J9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-LUB-260815</v>
       </c>
       <c r="K9" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>150</v>
       </c>
       <c r="L9" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>PCS</v>
       </c>
       <c r="M9" s="7">
         <v>150</v>
       </c>
       <c r="N9" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>PCS</v>
       </c>
       <c r="O9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-01</v>
       </c>
       <c r="P9" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>D-02-01-01</v>
       </c>
       <c r="Q9" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Hazardous</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>155</v>
       </c>
       <c r="S9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Hazardous</v>
       </c>
       <c r="T9" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U9" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V9" s="6"/>
       <c r="W9" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0003-10</v>
       </c>
     </row>
@@ -10609,7 +12285,7 @@
         <v>46249</v>
       </c>
       <c r="D10" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46249</v>
       </c>
       <c r="E10" s="6" t="s">
@@ -10619,66 +12295,66 @@
         <v>20</v>
       </c>
       <c r="G10" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0003-20</v>
       </c>
       <c r="H10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00013</v>
       </c>
       <c r="I10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Radiator Coolant 20L</v>
       </c>
       <c r="J10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-LUB-260815</v>
       </c>
       <c r="K10" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>80</v>
       </c>
       <c r="L10" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>LTR</v>
       </c>
       <c r="M10" s="7">
         <v>80</v>
       </c>
       <c r="N10" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>LTR</v>
       </c>
       <c r="O10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-01</v>
       </c>
       <c r="P10" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>D-02-01-02</v>
       </c>
       <c r="Q10" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Hazardous</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>159</v>
       </c>
       <c r="S10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Hazardous</v>
       </c>
       <c r="T10" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U10" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V10" s="6"/>
       <c r="W10" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0003-20</v>
       </c>
     </row>
@@ -10693,7 +12369,7 @@
         <v>46251</v>
       </c>
       <c r="D11" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46251</v>
       </c>
       <c r="E11" s="6" t="s">
@@ -10703,66 +12379,66 @@
         <v>10</v>
       </c>
       <c r="G11" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0004-10</v>
       </c>
       <c r="H11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00014</v>
       </c>
       <c r="I11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Flat Washer M12 Zinc Plated</v>
       </c>
       <c r="J11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-FST-260817</v>
       </c>
       <c r="K11" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>5000</v>
       </c>
       <c r="L11" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>PCS</v>
       </c>
       <c r="M11" s="7">
         <v>5000</v>
       </c>
       <c r="N11" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>PCS</v>
       </c>
       <c r="O11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-02</v>
       </c>
       <c r="P11" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>D-01-01-02</v>
       </c>
       <c r="Q11" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Standard</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>162</v>
       </c>
       <c r="S11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Standard</v>
       </c>
       <c r="T11" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U11" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V11" s="6"/>
       <c r="W11" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0004-10</v>
       </c>
     </row>
@@ -10777,7 +12453,7 @@
         <v>46251</v>
       </c>
       <c r="D12" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46251</v>
       </c>
       <c r="E12" s="6" t="s">
@@ -10787,66 +12463,66 @@
         <v>10</v>
       </c>
       <c r="G12" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0005-10</v>
       </c>
       <c r="H12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00005</v>
       </c>
       <c r="I12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Industrial Degreaser 20L</v>
       </c>
       <c r="J12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-CHM-260817</v>
       </c>
       <c r="K12" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>28</v>
       </c>
       <c r="L12" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>LTR</v>
       </c>
       <c r="M12" s="7">
         <v>28</v>
       </c>
       <c r="N12" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>LTR</v>
       </c>
       <c r="O12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-02</v>
       </c>
       <c r="P12" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>D-02-01-01</v>
       </c>
       <c r="Q12" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Hazardous</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>155</v>
       </c>
       <c r="S12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Hazardous</v>
       </c>
       <c r="T12" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U12" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V12" s="6"/>
       <c r="W12" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0005-10</v>
       </c>
     </row>
@@ -10861,7 +12537,7 @@
         <v>46253</v>
       </c>
       <c r="D13" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46253</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -10871,66 +12547,66 @@
         <v>20</v>
       </c>
       <c r="G13" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0006-20</v>
       </c>
       <c r="H13" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00018</v>
       </c>
       <c r="I13" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Cabin Air Filter</v>
       </c>
       <c r="J13" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-FLT-260819</v>
       </c>
       <c r="K13" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>50</v>
       </c>
       <c r="L13" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>PCS</v>
       </c>
       <c r="M13" s="7">
         <v>50</v>
       </c>
       <c r="N13" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>PCS</v>
       </c>
       <c r="O13" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-02</v>
       </c>
       <c r="P13" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>A-02-01-03</v>
       </c>
       <c r="Q13" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Standard</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>165</v>
       </c>
       <c r="S13" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Standard</v>
       </c>
       <c r="T13" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U13" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V13" s="6"/>
       <c r="W13" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0006-20</v>
       </c>
     </row>
@@ -10945,7 +12621,7 @@
         <v>46259</v>
       </c>
       <c r="D14" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46259</v>
       </c>
       <c r="E14" s="6" t="s">
@@ -10955,66 +12631,66 @@
         <v>10</v>
       </c>
       <c r="G14" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0007-10</v>
       </c>
       <c r="H14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00010</v>
       </c>
       <c r="I14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Welding Electrode E7018 3.2mm</v>
       </c>
       <c r="J14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-WLD-260825</v>
       </c>
       <c r="K14" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>250</v>
       </c>
       <c r="L14" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>KG</v>
       </c>
       <c r="M14" s="7">
         <v>250</v>
       </c>
       <c r="N14" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>KG</v>
       </c>
       <c r="O14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-01</v>
       </c>
       <c r="P14" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>D-01-01-02</v>
       </c>
       <c r="Q14" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Standard</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>162</v>
       </c>
       <c r="S14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Standard</v>
       </c>
       <c r="T14" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U14" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V14" s="6"/>
       <c r="W14" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0007-10</v>
       </c>
     </row>
@@ -11029,7 +12705,7 @@
         <v>46264</v>
       </c>
       <c r="D15" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46264</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -11039,66 +12715,66 @@
         <v>10</v>
       </c>
       <c r="G15" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0008-10</v>
       </c>
       <c r="H15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00002</v>
       </c>
       <c r="I15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Steel Plate 10mm x 2m x 1m</v>
       </c>
       <c r="J15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-STEEL-260830</v>
       </c>
       <c r="K15" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>20</v>
       </c>
       <c r="L15" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>PCS</v>
       </c>
       <c r="M15" s="7">
         <v>20</v>
       </c>
       <c r="N15" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>PCS</v>
       </c>
       <c r="O15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-01</v>
       </c>
       <c r="P15" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>C-01-01</v>
       </c>
       <c r="Q15" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Heavy/Bulk</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>269</v>
       </c>
       <c r="S15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Heavy/Bulk</v>
       </c>
       <c r="T15" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U15" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V15" s="6"/>
       <c r="W15" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0008-10</v>
       </c>
     </row>
@@ -11113,7 +12789,7 @@
         <v>46264</v>
       </c>
       <c r="D16" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46264</v>
       </c>
       <c r="E16" s="6" t="s">
@@ -11123,66 +12799,66 @@
         <v>20</v>
       </c>
       <c r="G16" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0008-20</v>
       </c>
       <c r="H16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00004</v>
       </c>
       <c r="I16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Hex Bolt M12x50 Grade 8.8</v>
       </c>
       <c r="J16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-BOLT-260830</v>
       </c>
       <c r="K16" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>2500</v>
       </c>
       <c r="L16" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>PCS</v>
       </c>
       <c r="M16" s="7">
         <v>2500</v>
       </c>
       <c r="N16" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>PCS</v>
       </c>
       <c r="O16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-01</v>
       </c>
       <c r="P16" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>D-01-01-01</v>
       </c>
       <c r="Q16" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Standard</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>154</v>
       </c>
       <c r="S16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Standard</v>
       </c>
       <c r="T16" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U16" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Completed</v>
       </c>
       <c r="V16" s="6"/>
       <c r="W16" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0008-20</v>
       </c>
     </row>
@@ -11197,7 +12873,7 @@
         <v>46273</v>
       </c>
       <c r="D17" s="64">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[GR Date])</f>
         <v>46273</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -11207,68 +12883,68 @@
         <v>10</v>
       </c>
       <c r="G17" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[GR Line]]</f>
         <v>GR-2026-0009-10</v>
       </c>
       <c r="H17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Material Code])</f>
         <v>MAT-00017</v>
       </c>
       <c r="I17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_GoodsReceipt[Material Code],[1]!tbl_GoodsReceipt[Material Description])</f>
         <v>Steel I-Beam 6m Length</v>
       </c>
       <c r="J17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Batch/Lot Number])</f>
         <v>LOT-STL-260908</v>
       </c>
       <c r="K17" s="12">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Accepted Qty])</f>
         <v>10</v>
       </c>
       <c r="L17" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Purchase UoM])</f>
         <v>PCS</v>
       </c>
       <c r="M17" s="7">
         <v>5</v>
       </c>
       <c r="N17" s="12" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
         <v>PCS</v>
       </c>
       <c r="O17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[GR Line Key (Helper)]],[1]!tbl_GoodsReceipt[GR Line Key (Helper)],[1]!tbl_GoodsReceipt[Receiving Dock])</f>
         <v>E-01</v>
       </c>
       <c r="P17" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Default Storage Location])</f>
         <v>C-01-02</v>
       </c>
       <c r="Q17" s="65" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Storage/Handling Class])</f>
         <v>Heavy/Bulk</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>270</v>
       </c>
       <c r="S17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</f>
+        <f>_xlfn.XLOOKUP(tbl_PutAway2[[#This Row],[To Location]],[1]!tbl_MasterLocation[Location Code],[1]!tbl_MasterLocation[Storage/Handling Requirement])</f>
         <v>Heavy/Bulk</v>
       </c>
       <c r="T17" s="66" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway2[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</f>
         <v>Match</v>
       </c>
       <c r="U17" s="16" t="str">
-        <f>IF(tbl_PutAway[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway[[#This Row],[Put Away Qty]]&lt;tbl_PutAway[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
+        <f>IF(tbl_PutAway2[[#This Row],[Put Away Qty]]=0,"Pending", IF(tbl_PutAway2[[#This Row],[Put Away Qty]]&lt;tbl_PutAway2[[#This Row],[Accepted Qty]],"Partial","Completed"))</f>
         <v>Partial</v>
       </c>
       <c r="V17" s="6" t="s">
         <v>317</v>
       </c>
       <c r="W17" s="17" t="str">
-        <f>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</f>
+        <f>tbl_PutAway2[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway2[[#This Row],[Put Away Line]]</f>
         <v>PA-2026-0009-10</v>
       </c>
     </row>
@@ -11490,28 +13166,28 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="Q18:Q509">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="22" priority="3">
       <formula>$Q18="Mismatch - Review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:T17">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>$T4="Mismatch - Review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4:U17">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="20" priority="2">
       <formula>$U4="Partial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="73">
+    <cfRule type="expression" dxfId="19" priority="4">
       <formula>$U4="Exception - Needs Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="74">
+    <cfRule type="expression" dxfId="18" priority="5">
       <formula>$U4="Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please select a value from the list." promptTitle="Putaway Location" prompt="Select an active, pickable storage location." sqref="M18:M25 M27:M509" xr:uid="{00000000-0002-0000-0500-000002000000}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please select a value from the list." promptTitle="Putaway Location" prompt="Select an active, pickable storage location." sqref="M27:M509 M18:M25" xr:uid="{00000000-0002-0000-0500-000002000000}">
       <formula1>"BLK-A-01,BLK-A-02,RCK-B-01-01,RCK-B-01-02,RCK-B-02-01,HAZ-C-01"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -11523,7 +13199,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please select a value from the list." promptTitle="GR Number" prompt="Select the GR Number this put-away is against." xr:uid="{00000000-0002-0000-0500-000000000000}">
           <x14:formula1>
             <xm:f>'05_Goods_Receipt'!$A$4:$A$17</xm:f>
@@ -11531,7 +13207,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D51:D509 E4:E17 D18:D29</xm:sqref>
+          <xm:sqref>D51:D509 D19:D29</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please select a value from the list." promptTitle="GR Line" prompt="Select the GR Line this put-away is against." xr:uid="{00000000-0002-0000-0500-000001000000}">
           <x14:formula1>
@@ -11540,19 +13216,13 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E51:E509 F4:F17 E18:E29</xm:sqref>
+          <xm:sqref>E51:E509 E19:E29</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please select a value from the list." promptTitle="Putaway Location" prompt="Select an active, pickable storage location." xr:uid="{8B2961C3-5CD8-466B-ABFE-53D3E96F4657}">
           <x14:formula1>
             <xm:f>'01_Master_Material'!$F$4:$F$23</xm:f>
           </x14:formula1>
           <xm:sqref>M26</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please select a value from the list." promptTitle="Putaway Location" prompt="Select an active, pickable storage location." xr:uid="{C9E9FDD9-6BAC-4170-8480-75639DB439E6}">
-          <x14:formula1>
-            <xm:f>'03_Master_Location'!$A$4:$A$27</xm:f>
-          </x14:formula1>
-          <xm:sqref>R4:R17</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11562,31 +13232,3021 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" customWidth="1"/>
+    <col min="17" max="17" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+    </row>
+    <row r="3" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4" s="8">
+        <v>46246</v>
+      </c>
+      <c r="D4" s="8">
+        <v>46248</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Hydraulic Cylinder Seal Kit 80mm</v>
+      </c>
+      <c r="I4" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J4" s="11">
+        <v>4</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="M4" s="16" t="str">
+        <f>IF(L4&gt;=J4,"Sufficient","Insufficient - Review")</f>
+        <v>Sufficient</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O4" s="3">
+        <f>SUMIF('[1]09_Goods_Issue'!$J:$J,G4,'[1]09_Goods_Issue'!$P:$P)</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0001-10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B5" s="7">
+        <v>20</v>
+      </c>
+      <c r="C5" s="8">
+        <v>46246</v>
+      </c>
+      <c r="D5" s="8">
+        <v>46248</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Hydraulic Hose 1/2in x 3m</v>
+      </c>
+      <c r="I5" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J5" s="11">
+        <v>20</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L5" s="19"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O5" s="3"/>
+      <c r="P5" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0001-20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B6" s="7">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8">
+        <v>46250</v>
+      </c>
+      <c r="D6" s="8">
+        <v>46252</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Engine Oil Filter (Cat 320D)</v>
+      </c>
+      <c r="I6" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J6" s="11">
+        <v>100</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="L6" s="19"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6" s="3"/>
+      <c r="P6" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="R6" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0002-10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B7" s="7">
+        <v>10</v>
+      </c>
+      <c r="C7" s="8">
+        <v>46252</v>
+      </c>
+      <c r="D7" s="8">
+        <v>46254</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Hex Bolt M12x50 Grade 8.8</v>
+      </c>
+      <c r="I7" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J7" s="11">
+        <v>3000</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L7" s="19"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O7" s="3"/>
+      <c r="P7" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0003-10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="B8" s="7">
+        <v>10</v>
+      </c>
+      <c r="C8" s="8">
+        <v>46254</v>
+      </c>
+      <c r="D8" s="8">
+        <v>46256</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Industrial Degreaser 20L</v>
+      </c>
+      <c r="I8" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>LTR</v>
+      </c>
+      <c r="J8" s="11">
+        <v>120</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L8" s="19"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="O8" s="3"/>
+      <c r="P8" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="R8" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0004-10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B9" s="7">
+        <v>10</v>
+      </c>
+      <c r="C9" s="8">
+        <v>46256</v>
+      </c>
+      <c r="D9" s="8">
+        <v>46258</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Welding Electrode E7018 3.2mm</v>
+      </c>
+      <c r="I9" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>KG</v>
+      </c>
+      <c r="J9" s="11">
+        <v>6</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="L9" s="19"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O9" s="3"/>
+      <c r="P9" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="R9" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0005-10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B10" s="7">
+        <v>20</v>
+      </c>
+      <c r="C10" s="8">
+        <v>46256</v>
+      </c>
+      <c r="D10" s="8">
+        <v>46258</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Flat Washer M12 Zinc Plated</v>
+      </c>
+      <c r="I10" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J10" s="11">
+        <v>9000</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L10" s="19"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O10" s="3"/>
+      <c r="P10" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0005-20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B11" s="7">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8">
+        <v>46259</v>
+      </c>
+      <c r="D11" s="8">
+        <v>46261</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Steel Plate 10mm x 2m x 1m</v>
+      </c>
+      <c r="I11" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J11" s="11">
+        <v>15</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L11" s="19"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O11" s="3"/>
+      <c r="P11" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="R11" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0006-10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B12" s="7">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8">
+        <v>46264</v>
+      </c>
+      <c r="D12" s="8">
+        <v>46266</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Final Drive Motor (Excavator PC200)</v>
+      </c>
+      <c r="I12" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J12" s="11">
+        <v>60</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L12" s="19"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="O12" s="3"/>
+      <c r="P12" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="R12" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0007-10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B13" s="7">
+        <v>10</v>
+      </c>
+      <c r="C13" s="8">
+        <v>46266</v>
+      </c>
+      <c r="D13" s="8">
+        <v>46268</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Air Filter Element - Primary</v>
+      </c>
+      <c r="I13" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J13" s="11">
+        <v>24</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L13" s="19"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O13" s="3"/>
+      <c r="P13" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0008-10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B14" s="7">
+        <v>10</v>
+      </c>
+      <c r="C14" s="8">
+        <v>46268</v>
+      </c>
+      <c r="D14" s="8">
+        <v>46270</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Track Roller Assembly</v>
+      </c>
+      <c r="I14" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J14" s="11">
+        <v>40</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="L14" s="19"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O14" s="3"/>
+      <c r="P14" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="R14" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0009-10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B15" s="7">
+        <v>10</v>
+      </c>
+      <c r="C15" s="8">
+        <v>46270</v>
+      </c>
+      <c r="D15" s="8">
+        <v>46272</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Grease Cartridge NLGI2 400g</v>
+      </c>
+      <c r="I15" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J15" s="11">
+        <v>200</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L15" s="19"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="O15" s="3">
+        <f>SUMIF('[1]09_Goods_Issue'!$J:$J,G15,'[1]09_Goods_Issue'!$P:$P)</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="R15" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0010-10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B16" s="7">
+        <v>20</v>
+      </c>
+      <c r="C16" s="8">
+        <v>46270</v>
+      </c>
+      <c r="D16" s="8">
+        <v>46272</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Bucket Teeth (CAT style)</v>
+      </c>
+      <c r="I16" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J16" s="11">
+        <v>36</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L16" s="19"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O16" s="3">
+        <f>SUMIF('[1]09_Goods_Issue'!$J:$J,G16,'[1]09_Goods_Issue'!$P:$P)</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0010-20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="B17" s="7">
+        <v>10</v>
+      </c>
+      <c r="C17" s="8">
+        <v>46273</v>
+      </c>
+      <c r="D17" s="8">
+        <v>46275</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Radiator Coolant 20L</v>
+      </c>
+      <c r="I17" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>LTR</v>
+      </c>
+      <c r="J17" s="11">
+        <v>80</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L17" s="19"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O17" s="3">
+        <f>SUMIF('[1]09_Goods_Issue'!$J:$J,G17,'[1]09_Goods_Issue'!$P:$P)</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="R17" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0011-10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B18" s="7">
+        <v>10</v>
+      </c>
+      <c r="C18" s="8">
+        <v>46275</v>
+      </c>
+      <c r="D18" s="8">
+        <v>46277</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Turbocharger Assembly (Cat C15)</v>
+      </c>
+      <c r="I18" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J18" s="11">
+        <v>150</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L18" s="19"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O18" s="3">
+        <f>SUMIF('[1]09_Goods_Issue'!$J:$J,G18,'[1]09_Goods_Issue'!$P:$P)</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="17" t="str">
+        <f>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0012-10</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="I19:I507">
+    <cfRule type="expression" dxfId="17" priority="1">
+      <formula>$I19="Urgent"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4:K18">
+    <cfRule type="expression" dxfId="16" priority="6">
+      <formula>$K4="Urgent"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:N18">
+    <cfRule type="expression" dxfId="15" priority="4">
+      <formula>$M4="Insufficient - Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="5">
+      <formula>$M4="Sufficient"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N19:N507">
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>$N19="Insufficient - Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="3">
+      <formula>$N19="Sufficient"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please select a value from the list." promptTitle="Requesting Department" prompt="Select the requesting department." sqref="C19:C21 C37:C507" xr:uid="{CDC93C4D-D7B7-4752-A9B3-3A4EAC69C6C7}">
+      <formula1>"Production,Maintenance,QC"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please select a value from the list." promptTitle="Request Status" prompt="Current status of this request line." sqref="O19:O507 P4:P18" xr:uid="{B2D72D1D-5701-4F83-8D72-B235CF3F052B}">
+      <formula1>"Open,Approved,Rejected,Fulfilled"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please select a value from the list." promptTitle="Requesting Department" prompt="Select the requesting department." sqref="E4:E18" xr:uid="{24E7F2C5-9CAE-438D-B0AF-33FF282410C8}">
+      <formula1>"Production,Assembly,Maintenance,QC,Engineering"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please select a value from the list." promptTitle="Request Priority" prompt="Routine or Urgent (machine-down) request." sqref="K4:K18 I19:I507" xr:uid="{A3227F8D-233B-4162-84E8-177CCACA7ABA}">
+      <formula1>"Routine,Urgent"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.140625" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" customWidth="1"/>
+    <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+    </row>
+    <row r="3" spans="1:19" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B4" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4" s="8">
+        <v>46247</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E4" s="7">
+        <v>10</v>
+      </c>
+      <c r="F4" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0001-10</v>
+      </c>
+      <c r="G4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</f>
+        <v>MAT-00001</v>
+      </c>
+      <c r="H4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</f>
+        <v>Hydraulic Cylinder Seal Kit 80mm</v>
+      </c>
+      <c r="I4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</f>
+        <v>Production</v>
+      </c>
+      <c r="K4" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</f>
+        <v>Routine</v>
+      </c>
+      <c r="L4" s="12">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</f>
+        <v>4</v>
+      </c>
+      <c r="M4" s="73" t="s">
+        <v>381</v>
+      </c>
+      <c r="N4" s="74" t="s">
+        <v>382</v>
+      </c>
+      <c r="O4" s="11">
+        <v>4</v>
+      </c>
+      <c r="P4" s="16" t="str">
+        <f>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</f>
+        <v>Fully Picked</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="R4" s="6"/>
+      <c r="S4" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</f>
+        <v>PL-2026-0001-10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B5" s="7">
+        <v>20</v>
+      </c>
+      <c r="C5" s="8">
+        <v>46247</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E5" s="7">
+        <v>20</v>
+      </c>
+      <c r="F5" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0001-20</v>
+      </c>
+      <c r="G5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</f>
+        <v>MAT-00008</v>
+      </c>
+      <c r="H5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</f>
+        <v>Hydraulic Hose 1/2in x 3m</v>
+      </c>
+      <c r="I5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</f>
+        <v>Production</v>
+      </c>
+      <c r="K5" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</f>
+        <v>Routine</v>
+      </c>
+      <c r="L5" s="12">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</f>
+        <v>20</v>
+      </c>
+      <c r="M5" s="73" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Material Code]],[1]!tbl_PutAway[Material Code],[1]!tbl_PutAway[To Location])</f>
+        <v>A-01-02-01</v>
+      </c>
+      <c r="N5" s="74"/>
+      <c r="O5" s="11">
+        <v>20</v>
+      </c>
+      <c r="P5" s="16" t="str">
+        <f>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</f>
+        <v>Fully Picked</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="R5" s="6"/>
+      <c r="S5" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</f>
+        <v>PL-2026-0001-20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="B6" s="7">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8">
+        <v>46251</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="E6" s="7">
+        <v>10</v>
+      </c>
+      <c r="F6" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0002-10</v>
+      </c>
+      <c r="G6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</f>
+        <v>MAT-00003</v>
+      </c>
+      <c r="H6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</f>
+        <v>Engine Oil Filter (Cat 320D)</v>
+      </c>
+      <c r="I6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</f>
+        <v>Maintenance</v>
+      </c>
+      <c r="K6" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</f>
+        <v>Urgent</v>
+      </c>
+      <c r="L6" s="12">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</f>
+        <v>100</v>
+      </c>
+      <c r="M6" s="73" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Material Code]],[1]!tbl_PutAway[Material Code],[1]!tbl_PutAway[To Location])</f>
+        <v>A-02-01-01</v>
+      </c>
+      <c r="N6" s="74"/>
+      <c r="O6" s="11">
+        <v>100</v>
+      </c>
+      <c r="P6" s="16" t="str">
+        <f>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</f>
+        <v>Fully Picked</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="S6" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</f>
+        <v>PL-2026-0002-10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="B7" s="7">
+        <v>10</v>
+      </c>
+      <c r="C7" s="8">
+        <v>46255</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E7" s="7">
+        <v>10</v>
+      </c>
+      <c r="F7" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0003-10</v>
+      </c>
+      <c r="G7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</f>
+        <v>MAT-00004</v>
+      </c>
+      <c r="H7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</f>
+        <v>Hex Bolt M12x50 Grade 8.8</v>
+      </c>
+      <c r="I7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</f>
+        <v>Production</v>
+      </c>
+      <c r="K7" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</f>
+        <v>Routine</v>
+      </c>
+      <c r="L7" s="12">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</f>
+        <v>3000</v>
+      </c>
+      <c r="M7" s="73" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Material Code]],[1]!tbl_PutAway[Material Code],[1]!tbl_PutAway[To Location])</f>
+        <v>D-01-01-01</v>
+      </c>
+      <c r="N7" s="74"/>
+      <c r="O7" s="11">
+        <v>3000</v>
+      </c>
+      <c r="P7" s="16" t="str">
+        <f>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</f>
+        <v>Fully Picked</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="R7" s="6"/>
+      <c r="S7" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</f>
+        <v>PL-2026-0003-10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B8" s="7">
+        <v>10</v>
+      </c>
+      <c r="C8" s="8">
+        <v>46257</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E8" s="7">
+        <v>10</v>
+      </c>
+      <c r="F8" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0005-10</v>
+      </c>
+      <c r="G8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</f>
+        <v>MAT-00010</v>
+      </c>
+      <c r="H8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</f>
+        <v>Welding Electrode E7018 3.2mm</v>
+      </c>
+      <c r="I8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</f>
+        <v>KG</v>
+      </c>
+      <c r="J8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</f>
+        <v>Production</v>
+      </c>
+      <c r="K8" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</f>
+        <v>Urgent</v>
+      </c>
+      <c r="L8" s="12">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</f>
+        <v>6</v>
+      </c>
+      <c r="M8" s="73" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Material Code]],[1]!tbl_PutAway[Material Code],[1]!tbl_PutAway[To Location])</f>
+        <v>D-01-01-02</v>
+      </c>
+      <c r="N8" s="74"/>
+      <c r="O8" s="11">
+        <v>6</v>
+      </c>
+      <c r="P8" s="16" t="str">
+        <f>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</f>
+        <v>Fully Picked</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="R8" s="6"/>
+      <c r="S8" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</f>
+        <v>PL-2026-0004-10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B9" s="7">
+        <v>20</v>
+      </c>
+      <c r="C9" s="8">
+        <v>46257</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E9" s="7">
+        <v>20</v>
+      </c>
+      <c r="F9" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0005-20</v>
+      </c>
+      <c r="G9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</f>
+        <v>MAT-00014</v>
+      </c>
+      <c r="H9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</f>
+        <v>Flat Washer M12 Zinc Plated</v>
+      </c>
+      <c r="I9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</f>
+        <v>Assembly</v>
+      </c>
+      <c r="K9" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</f>
+        <v>Routine</v>
+      </c>
+      <c r="L9" s="12">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</f>
+        <v>9000</v>
+      </c>
+      <c r="M9" s="73" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Material Code]],[1]!tbl_PutAway[Material Code],[1]!tbl_PutAway[To Location])</f>
+        <v>D-01-01-02</v>
+      </c>
+      <c r="N9" s="74"/>
+      <c r="O9" s="11">
+        <v>9000</v>
+      </c>
+      <c r="P9" s="16" t="str">
+        <f>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</f>
+        <v>Fully Picked</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="S9" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</f>
+        <v>PL-2026-0004-20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="B10" s="7">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8">
+        <v>46260</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="E10" s="7">
+        <v>10</v>
+      </c>
+      <c r="F10" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0006-10</v>
+      </c>
+      <c r="G10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</f>
+        <v>MAT-00002</v>
+      </c>
+      <c r="H10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</f>
+        <v>Steel Plate 10mm x 2m x 1m</v>
+      </c>
+      <c r="I10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</f>
+        <v>Maintenance</v>
+      </c>
+      <c r="K10" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</f>
+        <v>Routine</v>
+      </c>
+      <c r="L10" s="12">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</f>
+        <v>15</v>
+      </c>
+      <c r="M10" s="73" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Material Code]],[1]!tbl_PutAway[Material Code],[1]!tbl_PutAway[To Location])</f>
+        <v>C-01-01</v>
+      </c>
+      <c r="N10" s="74"/>
+      <c r="O10" s="11">
+        <v>15</v>
+      </c>
+      <c r="P10" s="16" t="str">
+        <f>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</f>
+        <v>Fully Picked</v>
+      </c>
+      <c r="Q10" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="R10" s="6"/>
+      <c r="S10" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</f>
+        <v>PL-2026-0005-10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B11" s="7">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8">
+        <v>46267</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E11" s="7">
+        <v>10</v>
+      </c>
+      <c r="F11" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0008-10</v>
+      </c>
+      <c r="G11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</f>
+        <v>MAT-00007</v>
+      </c>
+      <c r="H11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</f>
+        <v>Air Filter Element - Primary</v>
+      </c>
+      <c r="I11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</f>
+        <v>QC</v>
+      </c>
+      <c r="K11" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</f>
+        <v>Routine</v>
+      </c>
+      <c r="L11" s="12">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</f>
+        <v>24</v>
+      </c>
+      <c r="M11" s="73" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Material Code]],[1]!tbl_PutAway[Material Code],[1]!tbl_PutAway[To Location])</f>
+        <v>A-02-01-02</v>
+      </c>
+      <c r="N11" s="74"/>
+      <c r="O11" s="11">
+        <v>24</v>
+      </c>
+      <c r="P11" s="16" t="str">
+        <f>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</f>
+        <v>Fully Picked</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="S11" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</f>
+        <v>PL-2026-0006-10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B12" s="7">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8">
+        <v>46269</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E12" s="7">
+        <v>10</v>
+      </c>
+      <c r="F12" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0009-10</v>
+      </c>
+      <c r="G12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</f>
+        <v>MAT-00006</v>
+      </c>
+      <c r="H12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</f>
+        <v>Track Roller Assembly</v>
+      </c>
+      <c r="I12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</f>
+        <v>Production</v>
+      </c>
+      <c r="K12" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</f>
+        <v>Urgent</v>
+      </c>
+      <c r="L12" s="12">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</f>
+        <v>40</v>
+      </c>
+      <c r="M12" s="73" t="e">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Material Code]],[1]!tbl_PutAway[Material Code],[1]!tbl_PutAway[To Location])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N12" s="74">
+        <f>SUMIF('[1]06_Put_Away'!$F:$F,G12,'[1]06_Put_Away'!$I:$I)-SUMIF('[1]09_Goods_Issue'!$J:$J,G12,'[1]09_Goods_Issue'!$P:$P)</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="11">
+        <v>40</v>
+      </c>
+      <c r="P12" s="16" t="str">
+        <f>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</f>
+        <v>Fully Picked</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="S12" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</f>
+        <v>PL-2026-0007-10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="B13" s="7">
+        <v>10</v>
+      </c>
+      <c r="C13" s="8">
+        <v>46271</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="E13" s="7">
+        <v>20</v>
+      </c>
+      <c r="F13" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0010-20</v>
+      </c>
+      <c r="G13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</f>
+        <v>MAT-00012</v>
+      </c>
+      <c r="H13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</f>
+        <v>Bucket Teeth (CAT style)</v>
+      </c>
+      <c r="I13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</f>
+        <v>Production</v>
+      </c>
+      <c r="K13" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</f>
+        <v>Routine</v>
+      </c>
+      <c r="L13" s="12">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</f>
+        <v>36</v>
+      </c>
+      <c r="M13" s="73" t="e">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Material Code]],[1]!tbl_PutAway[Material Code],[1]!tbl_PutAway[To Location])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N13" s="74">
+        <f>SUMIF('[1]06_Put_Away'!$F:$F,G13,'[1]06_Put_Away'!$I:$I)-SUMIF('[1]09_Goods_Issue'!$J:$J,G13,'[1]09_Goods_Issue'!$P:$P)</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="11">
+        <v>36</v>
+      </c>
+      <c r="P13" s="16" t="str">
+        <f>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</f>
+        <v>Fully Picked</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="R13" s="6"/>
+      <c r="S13" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</f>
+        <v>PL-2026-0008-10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B14" s="7">
+        <v>10</v>
+      </c>
+      <c r="C14" s="8">
+        <v>46274</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E14" s="7">
+        <v>10</v>
+      </c>
+      <c r="F14" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0011-10</v>
+      </c>
+      <c r="G14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</f>
+        <v>MAT-00013</v>
+      </c>
+      <c r="H14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</f>
+        <v>Radiator Coolant 20L</v>
+      </c>
+      <c r="I14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</f>
+        <v>LTR</v>
+      </c>
+      <c r="J14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</f>
+        <v>Maintenance</v>
+      </c>
+      <c r="K14" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</f>
+        <v>Routine</v>
+      </c>
+      <c r="L14" s="12">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</f>
+        <v>80</v>
+      </c>
+      <c r="M14" s="73" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Material Code]],[1]!tbl_PutAway[Material Code],[1]!tbl_PutAway[To Location])</f>
+        <v>D-02-01-02</v>
+      </c>
+      <c r="N14" s="74">
+        <f>SUMIF('[1]06_Put_Away'!$F:$F,G14,'[1]06_Put_Away'!$I:$I)-SUMIF('[1]09_Goods_Issue'!$J:$J,G14,'[1]09_Goods_Issue'!$P:$P)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="11">
+        <v>80</v>
+      </c>
+      <c r="P14" s="16" t="str">
+        <f>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</f>
+        <v>Fully Picked</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="S14" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</f>
+        <v>PL-2026-0009-10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="B15" s="7">
+        <v>10</v>
+      </c>
+      <c r="C15" s="8">
+        <v>46276</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="E15" s="7">
+        <v>10</v>
+      </c>
+      <c r="F15" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Request Line]]</f>
+        <v>MR-2026-0012-10</v>
+      </c>
+      <c r="G15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Code])</f>
+        <v>MAT-00015</v>
+      </c>
+      <c r="H15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Material Description])</f>
+        <v>Turbocharger Assembly (Cat C15)</v>
+      </c>
+      <c r="I15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="J15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Requesting Department])</f>
+        <v>Production</v>
+      </c>
+      <c r="K15" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Request Priority])</f>
+        <v>Routine</v>
+      </c>
+      <c r="L15" s="12">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Request Line Key (Helper)]],[1]!tbl_MaterialRequest[Request Line Key (Helper)],[1]!tbl_MaterialRequest[Quantity Requested])</f>
+        <v>150</v>
+      </c>
+      <c r="M15" s="73" t="e">
+        <f>_xlfn.XLOOKUP(tbl_PickingList11[[#This Row],[Material Code]],[1]!tbl_PutAway[Material Code],[1]!tbl_PutAway[To Location])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N15" s="74">
+        <f>SUMIF('[1]06_Put_Away'!$F:$F,G15,'[1]06_Put_Away'!$I:$I)-SUMIF('[1]09_Goods_Issue'!$J:$J,G15,'[1]09_Goods_Issue'!$P:$P)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="11">
+        <v>150</v>
+      </c>
+      <c r="P15" s="16" t="str">
+        <f>IF(tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList11[[#This Row],[Quantity Picked]]&lt;tbl_PickingList11[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</f>
+        <v>Fully Picked</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="R15" s="6"/>
+      <c r="S15" s="17" t="str">
+        <f>tbl_PickingList11[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList11[[#This Row],[Pick Line]]</f>
+        <v>PL-2026-0010-10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:S1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="K4:K27">
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>$K4="Urgent"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P4:P15">
+    <cfRule type="expression" dxfId="10" priority="6">
+      <formula>$P4="Fully Picked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P4:Q15">
+    <cfRule type="expression" dxfId="9" priority="5">
+      <formula>$P4="Partially Picked"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="7">
+      <formula>$P4="Not Picked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q16:Q27">
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>$Q16="Partially Picked"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="3">
+      <formula>$Q16="Fully Picked"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="4">
+      <formula>$Q16="Not Picked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="Q4:Q15" xr:uid="{8AD08929-3863-471E-A187-8175D91F2E55}">
+      <formula1>"Andi,Budi,Rizky,Dimas"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="46" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
+        <v>397</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+    </row>
+    <row r="3" spans="1:22" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B4" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4" s="8">
+        <v>46247</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="E4" s="7">
+        <v>10</v>
+      </c>
+      <c r="F4" s="8" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</f>
+        <v>MR-2026-0001</v>
+      </c>
+      <c r="G4" s="7">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</f>
+        <v>10</v>
+      </c>
+      <c r="H4" s="17" t="str">
+        <f>D4&amp;"-"&amp;E4</f>
+        <v>PL-2026-0001-10</v>
+      </c>
+      <c r="I4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</f>
+        <v>MAT-00001</v>
+      </c>
+      <c r="J4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Hydraulic Cylinder Seal Kit 80mm</v>
+      </c>
+      <c r="K4" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="L4" s="75" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</f>
+        <v>DaDari Stock Card</v>
+      </c>
+      <c r="M4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</f>
+        <v>Production</v>
+      </c>
+      <c r="N4" s="12">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</f>
+        <v>4</v>
+      </c>
+      <c r="O4" s="11">
+        <v>4</v>
+      </c>
+      <c r="P4" s="19">
+        <f>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="66" t="str">
+        <f>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</f>
+        <v>Completed</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="S4" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="T4" s="6"/>
+      <c r="U4" s="17" t="str">
+        <f>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</f>
+        <v>GI-2026-0001-10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B5" s="7">
+        <v>20</v>
+      </c>
+      <c r="C5" s="8">
+        <v>46247</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="E5" s="7">
+        <v>20</v>
+      </c>
+      <c r="F5" s="8" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</f>
+        <v>MR-2026-0001</v>
+      </c>
+      <c r="G5" s="7">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</f>
+        <v>20</v>
+      </c>
+      <c r="H5" s="17" t="str">
+        <f>D5&amp;"-"&amp;E5</f>
+        <v>PL-2026-0001-20</v>
+      </c>
+      <c r="I5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</f>
+        <v>MAT-00008</v>
+      </c>
+      <c r="J5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Hydraulic Hose 1/2in x 3m</v>
+      </c>
+      <c r="K5" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="L5" s="75" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</f>
+        <v>A-01-02-01</v>
+      </c>
+      <c r="M5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</f>
+        <v>Production</v>
+      </c>
+      <c r="N5" s="12">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</f>
+        <v>20</v>
+      </c>
+      <c r="O5" s="11">
+        <v>20</v>
+      </c>
+      <c r="P5" s="19">
+        <f>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="66" t="str">
+        <f>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</f>
+        <v>Completed</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="T5" s="6"/>
+      <c r="U5" s="17" t="str">
+        <f>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</f>
+        <v>GI-2026-0001-20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" s="7">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8">
+        <v>46251</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="E6" s="7">
+        <v>10</v>
+      </c>
+      <c r="F6" s="76" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</f>
+        <v>MR-2026-0002</v>
+      </c>
+      <c r="G6" s="77">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</f>
+        <v>10</v>
+      </c>
+      <c r="H6" s="78" t="str">
+        <f t="shared" ref="H6:H12" si="0">D6&amp;"-"&amp;E6</f>
+        <v>PL-2026-0002-10</v>
+      </c>
+      <c r="I6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</f>
+        <v>MAT-00003</v>
+      </c>
+      <c r="J6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Engine Oil Filter (Cat 320D)</v>
+      </c>
+      <c r="K6" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="L6" s="75" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</f>
+        <v>A-02-01-01</v>
+      </c>
+      <c r="M6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</f>
+        <v>Maintenance</v>
+      </c>
+      <c r="N6" s="12">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</f>
+        <v>100</v>
+      </c>
+      <c r="O6" s="11">
+        <v>100</v>
+      </c>
+      <c r="P6" s="19">
+        <f>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="79" t="str">
+        <f>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</f>
+        <v>Completed</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="U6" s="17" t="str">
+        <f>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</f>
+        <v>GI-2026-0002-10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" s="7">
+        <v>10</v>
+      </c>
+      <c r="C7" s="8">
+        <v>46255</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="E7" s="7">
+        <v>10</v>
+      </c>
+      <c r="F7" s="76" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</f>
+        <v>MR-2026-0003</v>
+      </c>
+      <c r="G7" s="77">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</f>
+        <v>10</v>
+      </c>
+      <c r="H7" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>PL-2026-0003-10</v>
+      </c>
+      <c r="I7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</f>
+        <v>MAT-00004</v>
+      </c>
+      <c r="J7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Hex Bolt M12x50 Grade 8.8</v>
+      </c>
+      <c r="K7" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="L7" s="75" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</f>
+        <v>D-01-01-01</v>
+      </c>
+      <c r="M7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</f>
+        <v>Production</v>
+      </c>
+      <c r="N7" s="12">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</f>
+        <v>3000</v>
+      </c>
+      <c r="O7" s="11">
+        <v>3000</v>
+      </c>
+      <c r="P7" s="19">
+        <f>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="79" t="str">
+        <f>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</f>
+        <v>Completed</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="S7" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="T7" s="6"/>
+      <c r="U7" s="17" t="str">
+        <f>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</f>
+        <v>GI-2026-0003-10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B8" s="7">
+        <v>10</v>
+      </c>
+      <c r="C8" s="8">
+        <v>46257</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E8" s="7">
+        <v>10</v>
+      </c>
+      <c r="F8" s="76" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</f>
+        <v>MR-2026-0005</v>
+      </c>
+      <c r="G8" s="77">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</f>
+        <v>10</v>
+      </c>
+      <c r="H8" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>PL-2026-0004-10</v>
+      </c>
+      <c r="I8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</f>
+        <v>MAT-00010</v>
+      </c>
+      <c r="J8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Welding Electrode E7018 3.2mm</v>
+      </c>
+      <c r="K8" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>KG</v>
+      </c>
+      <c r="L8" s="75" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</f>
+        <v>D-01-01-02</v>
+      </c>
+      <c r="M8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</f>
+        <v>Production</v>
+      </c>
+      <c r="N8" s="12">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</f>
+        <v>6</v>
+      </c>
+      <c r="O8" s="11">
+        <v>6</v>
+      </c>
+      <c r="P8" s="19">
+        <f>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="79" t="str">
+        <f>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</f>
+        <v>Completed</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="T8" s="6"/>
+      <c r="U8" s="17" t="str">
+        <f>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</f>
+        <v>GI-2026-0004-10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B9" s="7">
+        <v>20</v>
+      </c>
+      <c r="C9" s="8">
+        <v>46257</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E9" s="7">
+        <v>20</v>
+      </c>
+      <c r="F9" s="76" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</f>
+        <v>MR-2026-0005</v>
+      </c>
+      <c r="G9" s="77">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</f>
+        <v>20</v>
+      </c>
+      <c r="H9" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>PL-2026-0004-20</v>
+      </c>
+      <c r="I9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</f>
+        <v>MAT-00014</v>
+      </c>
+      <c r="J9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Flat Washer M12 Zinc Plated</v>
+      </c>
+      <c r="K9" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="L9" s="75" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</f>
+        <v>D-01-01-02</v>
+      </c>
+      <c r="M9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</f>
+        <v>Assembly</v>
+      </c>
+      <c r="N9" s="12">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</f>
+        <v>9000</v>
+      </c>
+      <c r="O9" s="11">
+        <v>8995</v>
+      </c>
+      <c r="P9" s="19">
+        <f>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</f>
+        <v>-5</v>
+      </c>
+      <c r="Q9" s="79" t="str">
+        <f>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</f>
+        <v>Partial</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="T9" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="U9" s="17" t="str">
+        <f>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</f>
+        <v>GI-2026-0004-20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="B10" s="7">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8">
+        <v>46260</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="E10" s="7">
+        <v>10</v>
+      </c>
+      <c r="F10" s="76" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</f>
+        <v>MR-2026-0006</v>
+      </c>
+      <c r="G10" s="77">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</f>
+        <v>10</v>
+      </c>
+      <c r="H10" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>PL-2026-0005-10</v>
+      </c>
+      <c r="I10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</f>
+        <v>MAT-00002</v>
+      </c>
+      <c r="J10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Steel Plate 10mm x 2m x 1m</v>
+      </c>
+      <c r="K10" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="L10" s="75" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</f>
+        <v>C-01-01</v>
+      </c>
+      <c r="M10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</f>
+        <v>Maintenance</v>
+      </c>
+      <c r="N10" s="12">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</f>
+        <v>15</v>
+      </c>
+      <c r="O10" s="11">
+        <v>15</v>
+      </c>
+      <c r="P10" s="19">
+        <f>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="79" t="str">
+        <f>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</f>
+        <v>Completed</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="T10" s="6"/>
+      <c r="U10" s="17" t="str">
+        <f>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</f>
+        <v>GI-2026-0005-10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B11" s="7">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8">
+        <v>46267</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E11" s="7">
+        <v>10</v>
+      </c>
+      <c r="F11" s="76" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</f>
+        <v>MR-2026-0008</v>
+      </c>
+      <c r="G11" s="77">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</f>
+        <v>10</v>
+      </c>
+      <c r="H11" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>PL-2026-0006-10</v>
+      </c>
+      <c r="I11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</f>
+        <v>MAT-00007</v>
+      </c>
+      <c r="J11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Air Filter Element - Primary</v>
+      </c>
+      <c r="K11" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="L11" s="75" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</f>
+        <v>A-02-01-02</v>
+      </c>
+      <c r="M11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</f>
+        <v>QC</v>
+      </c>
+      <c r="N11" s="12">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</f>
+        <v>24</v>
+      </c>
+      <c r="O11" s="11">
+        <v>24</v>
+      </c>
+      <c r="P11" s="19">
+        <f>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="79" t="str">
+        <f>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</f>
+        <v>Completed</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="T11" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="U11" s="17" t="str">
+        <f>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</f>
+        <v>GI-2026-0006-10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="B12" s="7">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8">
+        <v>46269</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="E12" s="7">
+        <v>10</v>
+      </c>
+      <c r="F12" s="76" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</f>
+        <v>MR-2026-0009</v>
+      </c>
+      <c r="G12" s="77">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</f>
+        <v>10</v>
+      </c>
+      <c r="H12" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>PL-2026-0007-10</v>
+      </c>
+      <c r="I12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</f>
+        <v>MAT-00006</v>
+      </c>
+      <c r="J12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Track Roller Assembly</v>
+      </c>
+      <c r="K12" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="L12" s="75" t="e">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</f>
+        <v>Production</v>
+      </c>
+      <c r="N12" s="12">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</f>
+        <v>40</v>
+      </c>
+      <c r="O12" s="11">
+        <v>40</v>
+      </c>
+      <c r="P12" s="19">
+        <f>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="79" t="str">
+        <f>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</f>
+        <v>Completed</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S12" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="T12" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="U12" s="17" t="str">
+        <f>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</f>
+        <v>GI-2026-0007-10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="B13" s="7">
+        <v>10</v>
+      </c>
+      <c r="C13" s="8">
+        <v>46271</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="E13" s="7">
+        <v>10</v>
+      </c>
+      <c r="F13" s="8" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</f>
+        <v>MR-2026-0010</v>
+      </c>
+      <c r="G13" s="7">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</f>
+        <v>20</v>
+      </c>
+      <c r="H13" s="17" t="str">
+        <f>D13&amp;"-"&amp;E13</f>
+        <v>PL-2026-0008-10</v>
+      </c>
+      <c r="I13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</f>
+        <v>MAT-00012</v>
+      </c>
+      <c r="J13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Bucket Teeth (CAT style)</v>
+      </c>
+      <c r="K13" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="L13" s="75" t="e">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</f>
+        <v>Production</v>
+      </c>
+      <c r="N13" s="12">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</f>
+        <v>36</v>
+      </c>
+      <c r="O13" s="11">
+        <v>36</v>
+      </c>
+      <c r="P13" s="19">
+        <f>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="66" t="str">
+        <f>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</f>
+        <v>Completed</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S13" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="T13" s="6"/>
+      <c r="U13" s="17" t="str">
+        <f>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</f>
+        <v>GI-2026-0008-10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B14" s="7">
+        <v>10</v>
+      </c>
+      <c r="C14" s="8">
+        <v>46274</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="E14" s="7">
+        <v>10</v>
+      </c>
+      <c r="F14" s="8" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</f>
+        <v>MR-2026-0011</v>
+      </c>
+      <c r="G14" s="7">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</f>
+        <v>10</v>
+      </c>
+      <c r="H14" s="17" t="str">
+        <f>D14&amp;"-"&amp;E14</f>
+        <v>PL-2026-0009-10</v>
+      </c>
+      <c r="I14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</f>
+        <v>MAT-00013</v>
+      </c>
+      <c r="J14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Radiator Coolant 20L</v>
+      </c>
+      <c r="K14" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>LTR</v>
+      </c>
+      <c r="L14" s="75" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</f>
+        <v>D-02-01-02</v>
+      </c>
+      <c r="M14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</f>
+        <v>Maintenance</v>
+      </c>
+      <c r="N14" s="12">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</f>
+        <v>80</v>
+      </c>
+      <c r="O14" s="11">
+        <v>80</v>
+      </c>
+      <c r="P14" s="19">
+        <f>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="66" t="str">
+        <f>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</f>
+        <v>Completed</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="S14" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="T14" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="U14" s="17" t="str">
+        <f>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</f>
+        <v>GI-2026-0009-10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="B15" s="7">
+        <v>10</v>
+      </c>
+      <c r="C15" s="8">
+        <v>46276</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="E15" s="7">
+        <v>10</v>
+      </c>
+      <c r="F15" s="8" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Number])</f>
+        <v>MR-2026-0012</v>
+      </c>
+      <c r="G15" s="7">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Request Line])</f>
+        <v>10</v>
+      </c>
+      <c r="H15" s="17" t="str">
+        <f>D15&amp;"-"&amp;E15</f>
+        <v>PL-2026-0010-10</v>
+      </c>
+      <c r="I15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Material Code])</f>
+        <v>MAT-00015</v>
+      </c>
+      <c r="J15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Material Description])</f>
+        <v>Turbocharger Assembly (Cat C15)</v>
+      </c>
+      <c r="K15" s="10" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],[1]!tbl_MasterMaterial[Material Code],[1]!tbl_MasterMaterial[Base UoM])</f>
+        <v>PCS</v>
+      </c>
+      <c r="L15" s="75" t="e">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Pick Location (Ref)])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="M15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Requesting Department (Ref)])</f>
+        <v>Production</v>
+      </c>
+      <c r="N15" s="12">
+        <f>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],[1]!tbl_PickingList[Pick Line Key (Helper)],[1]!tbl_PickingList[Quantity Picked])</f>
+        <v>150</v>
+      </c>
+      <c r="O15" s="11">
+        <v>150</v>
+      </c>
+      <c r="P15" s="19">
+        <f>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="66" t="str">
+        <f>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</f>
+        <v>Completed</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="T15" s="6"/>
+      <c r="U15" s="17" t="str">
+        <f>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</f>
+        <v>GI-2026-0010-10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:V1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="P4:Q15">
+    <cfRule type="expression" dxfId="4" priority="3">
+      <formula>$P4&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q4:Q15">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$Q4="Completed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q4:S15">
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>#REF!&lt;&gt;"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q16:S18">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>#REF!&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T16:T18">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$T16&lt;&gt;"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="R4:R15" xr:uid="{8EACE3EE-9719-405F-8974-4D6EA0955334}">
+      <formula1>"Andi,Budi,Rizky,Dimas"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q4:Q15" xr:uid="{398E02D3-CAAB-4C5B-9171-B601E03BF6DA}">
+      <formula1>"Partial,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please select a value from the list." promptTitle="Issue Variance Reason" prompt="Reason if Quantity Issued is less than Quantity Picked." sqref="T16:T18" xr:uid="{2CC39F07-FE0D-45E2-8F12-F49E1ECAB3C3}">
+      <formula1>"N/A,Damaged During Staging,Department Cancelled Partial Need,Recount Adjustment"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/Warehouse_Operations_Simulation.xlsx
+++ b/Warehouse_Operations_Simulation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Upgrade skill\1. Excel - Data Analytics\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C643BF5E-8E1F-4ADF-874B-F23B752043BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700275E2-3C0F-4E86-A8FD-1C0B2EE12777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2063,7 +2063,93 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="199">
+  <dxfs count="203">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <i/>
@@ -5251,21 +5337,21 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tbl_MasterMaterial" displayName="tbl_MasterMaterial" ref="A3:O23" totalsRowShown="0">
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Material Code" dataDxfId="198"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Material Description" dataDxfId="197"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Material Group" dataDxfId="196"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Material Code" dataDxfId="202"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Material Description" dataDxfId="201"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Material Group" dataDxfId="200"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Base UoM"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Primary Supplier Code"/>
-    <tableColumn id="24" xr3:uid="{0F116849-4911-4B80-B390-3C1C1D0A9D49}" name="Default Storage Location" dataDxfId="195"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Standard Cost (per Base UoM)" dataDxfId="194"/>
-    <tableColumn id="5" xr3:uid="{01500A3B-77EE-4BAE-BC67-664F09E22186}" name="ABC Classification" dataDxfId="193"/>
+    <tableColumn id="24" xr3:uid="{0F116849-4911-4B80-B390-3C1C1D0A9D49}" name="Default Storage Location" dataDxfId="199"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Standard Cost (per Base UoM)" dataDxfId="198"/>
+    <tableColumn id="5" xr3:uid="{01500A3B-77EE-4BAE-BC67-664F09E22186}" name="ABC Classification" dataDxfId="197"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Criticality Flag"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Storage/Handling Class"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Min Stock Level"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Max Stock Level"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Min Stock Level" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Max Stock Level" dataDxfId="0"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Lead Time (Days)"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Status"/>
-    <tableColumn id="22" xr3:uid="{BC7C3BEF-CB66-4A5F-9E71-E29F8E60C070}" name="Remarks" dataDxfId="192"/>
+    <tableColumn id="22" xr3:uid="{BC7C3BEF-CB66-4A5F-9E71-E29F8E60C070}" name="Remarks" dataDxfId="196"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5279,36 +5365,36 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Count Line"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Count Date"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="Material Code"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="Material Description" dataDxfId="96">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="Material Description" dataDxfId="100">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_CycleCount[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{42D72B1C-0469-448F-89C5-AE97F1EFA4A3}" name="ABC Classification" dataDxfId="95">
+    <tableColumn id="20" xr3:uid="{42D72B1C-0469-448F-89C5-AE97F1EFA4A3}" name="ABC Classification" dataDxfId="99">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_CycleCount[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[ABC Classification])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="Count Location (Ref)" dataDxfId="94"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="System Qty (Ref)" dataDxfId="93">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="Count Location (Ref)" dataDxfId="98"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="System Qty (Ref)" dataDxfId="97">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_CycleCount[[#This Row],[Material Code]],'10_Stock_Card'!F4:F32,'10_Stock_Card'!M4:M32,"",,-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0A00-00000A000000}" name="Physical Count" dataDxfId="92"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0A00-00000B000000}" name="Variance (Qty)" dataDxfId="91">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0A00-00000A000000}" name="Physical Count" dataDxfId="96"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0A00-00000B000000}" name="Variance (Qty)" dataDxfId="95">
       <calculatedColumnFormula>tbl_CycleCount[[#This Row],[Physical Count]]-tbl_CycleCount[[#This Row],[System Qty (Ref)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0A00-00000C000000}" name="Variance %" dataDxfId="90">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0A00-00000C000000}" name="Variance %" dataDxfId="94">
       <calculatedColumnFormula>IFERROR(tbl_CycleCount[[#This Row],[Variance (Qty)]]/tbl_CycleCount[[#This Row],[System Qty (Ref)]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0A00-00000D000000}" name="Unit Cost (Ref)" dataDxfId="89">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0A00-00000D000000}" name="Unit Cost (Ref)" dataDxfId="93">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_CycleCount[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Standard Cost (per Base UoM)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0A00-00000E000000}" name="Variance Value" dataDxfId="88">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0A00-00000E000000}" name="Variance Value" dataDxfId="92">
       <calculatedColumnFormula>tbl_CycleCount[[#This Row],[Variance (Qty)]]*tbl_CycleCount[[#This Row],[Unit Cost (Ref)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0A00-00000F000000}" name="Count Result" dataDxfId="87"/>
-    <tableColumn id="7" xr3:uid="{19FA728F-5901-4A45-82C7-A24BD8CD672D}" name="Count By" dataDxfId="86"/>
-    <tableColumn id="6" xr3:uid="{40535110-8F23-4B6C-8557-AF648D9A2B41}" name="Verified By" dataDxfId="85"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0A00-000010000000}" name="Root Cause" dataDxfId="84"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0A00-00000F000000}" name="Count Result" dataDxfId="91"/>
+    <tableColumn id="7" xr3:uid="{19FA728F-5901-4A45-82C7-A24BD8CD672D}" name="Count By" dataDxfId="90"/>
+    <tableColumn id="6" xr3:uid="{40535110-8F23-4B6C-8557-AF648D9A2B41}" name="Verified By" dataDxfId="89"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0A00-000010000000}" name="Root Cause" dataDxfId="88"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0A00-000011000000}" name="Adjustment Status"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0A00-000012000000}" name="Remarks"/>
-    <tableColumn id="19" xr3:uid="{2718145A-3CE3-42EB-A2A9-5B850CE78E6D}" name="Count Line Key (Helper)" dataDxfId="83">
+    <tableColumn id="19" xr3:uid="{2718145A-3CE3-42EB-A2A9-5B850CE78E6D}" name="Count Line Key (Helper)" dataDxfId="87">
       <calculatedColumnFormula>tbl_CycleCount[[#This Row],[Count Number]]&amp;"-"&amp;tbl_CycleCount[[#This Row],[Count Line]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5341,7 +5427,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Location Code"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Location Description"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Zone"/>
-    <tableColumn id="8" xr3:uid="{276A2345-C837-4FC6-B4E0-FF35EB523268}" name="Location Type" dataDxfId="191"/>
+    <tableColumn id="8" xr3:uid="{276A2345-C837-4FC6-B4E0-FF35EB523268}" name="Location Type" dataDxfId="195"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Storage/Handling Requirement"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Pickable Flag"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Capacity (Max Qty)"/>
@@ -5362,37 +5448,37 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="PO Line"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="PO Date"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Supplier Code"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Supplier Name" dataDxfId="190">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Supplier Name" dataDxfId="194">
       <calculatedColumnFormula>VLOOKUP(tbl_PurchaseOrder[[#This Row],[Supplier Code]],tbl_MasterSupplier[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Material Code"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Material Description" dataDxfId="189">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Material Description" dataDxfId="193">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PurchaseOrder[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Purchase UoM" dataDxfId="188"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Ordered Qty" dataDxfId="187" totalsRowDxfId="186"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Unit Price" dataDxfId="185" totalsRowDxfId="184"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Line Total" dataDxfId="183" totalsRowDxfId="182">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Purchase UoM" dataDxfId="192"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Ordered Qty" dataDxfId="191" totalsRowDxfId="190"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Unit Price" dataDxfId="189" totalsRowDxfId="188"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Line Total" dataDxfId="187" totalsRowDxfId="186">
       <calculatedColumnFormula>tbl_PurchaseOrder[[#This Row],[Ordered Qty]]*J4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="Order Priority" dataDxfId="181" totalsRowDxfId="180"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="Order Priority" dataDxfId="185" totalsRowDxfId="184"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="Lead Time (Days)">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PurchaseOrder[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Lead Time (Days)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="Expected Delivery Date" dataDxfId="179">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="Expected Delivery Date" dataDxfId="183">
       <calculatedColumnFormula>tbl_PurchaseOrder[[#This Row],[PO Date]]+tbl_PurchaseOrder[[#This Row],[Lead Time (Days)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{09E53041-1B48-4B81-BCF8-287332AE53AE}" name="Received Qty" dataDxfId="178" totalsRowDxfId="177">
+    <tableColumn id="13" xr3:uid="{09E53041-1B48-4B81-BCF8-287332AE53AE}" name="Received Qty" dataDxfId="182" totalsRowDxfId="181">
       <calculatedColumnFormula>SUMIFS(tbl_GoodsReceipt[Received Qty],tbl_GoodsReceipt[PO Line Key (Helper)],tbl_PurchaseOrder[[#This Row],[PO Line Key (Helper)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{123695AE-1CB2-4070-BEE2-29FE092ACFA7}" name="Outstanding Qty" dataDxfId="176" totalsRowDxfId="175">
+    <tableColumn id="14" xr3:uid="{123695AE-1CB2-4070-BEE2-29FE092ACFA7}" name="Outstanding Qty" dataDxfId="180" totalsRowDxfId="179">
       <calculatedColumnFormula>IFERROR(tbl_PurchaseOrder[[#This Row],[Received Qty]]-tbl_PurchaseOrder[[#This Row],[Ordered Qty]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="PO Status" dataDxfId="174">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="PO Status" dataDxfId="178">
       <calculatedColumnFormula>IF(tbl_PurchaseOrder[[#This Row],[Received Qty]]=0,"Open",IF(tbl_PurchaseOrder[[#This Row],[Received Qty]]&lt;tbl_PurchaseOrder[[#This Row],[Ordered Qty]],"Partial", "Closed"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Remarks" dataDxfId="173"/>
-    <tableColumn id="19" xr3:uid="{195CE6D1-9D3F-4D81-9DE2-B82EEBF35742}" name="PO Line Key (Helper)" dataDxfId="172" totalsRowDxfId="171">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Remarks" dataDxfId="177"/>
+    <tableColumn id="19" xr3:uid="{195CE6D1-9D3F-4D81-9DE2-B82EEBF35742}" name="PO Line Key (Helper)" dataDxfId="176" totalsRowDxfId="175">
       <calculatedColumnFormula>tbl_PurchaseOrder[[#This Row],[PO Number]]&amp;"-"&amp;tbl_PurchaseOrder[[#This Row],[PO Line]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5411,52 +5497,52 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="GR Line"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="GR Date"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="PO Number"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="PO Line" dataDxfId="170"/>
-    <tableColumn id="29" xr3:uid="{32467FAF-3D7D-4CA5-9707-3FB4E795D1FA}" name="PO Line Key (Helper)" dataDxfId="169">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="PO Line" dataDxfId="174"/>
+    <tableColumn id="29" xr3:uid="{32467FAF-3D7D-4CA5-9707-3FB4E795D1FA}" name="PO Line Key (Helper)" dataDxfId="173">
       <calculatedColumnFormula>tbl_GoodsReceipt[[#This Row],[PO Number]]&amp;"-"&amp;tbl_GoodsReceipt[[#This Row],[PO Line]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E8DA1EE4-E020-4801-93F4-A35A7E1B2656}" name="Supplier Code" dataDxfId="168">
+    <tableColumn id="6" xr3:uid="{E8DA1EE4-E020-4801-93F4-A35A7E1B2656}" name="Supplier Code" dataDxfId="172">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Supplier Code])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Supplier Name" dataDxfId="167">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Supplier Name" dataDxfId="171">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[Supplier Code]],tbl_MasterSupplier[Supplier Code],tbl_MasterSupplier[Supplier Name])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Material Code" dataDxfId="166">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Material Code" dataDxfId="170">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Material Code])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Material Description" dataDxfId="165">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Material Description" dataDxfId="169">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="Order Qty" dataDxfId="164">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="Order Qty" dataDxfId="168">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Ordered Qty])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="Purchase UoM" dataDxfId="163">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="Purchase UoM" dataDxfId="167">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Purchase UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="Unit Price" dataDxfId="162">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="Unit Price" dataDxfId="166">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Unit Price])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" name="Expected Delivery Date" dataDxfId="161">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" name="Expected Delivery Date" dataDxfId="165">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Expected Delivery Date])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{76F9E9A1-1F34-4FAD-9BFD-02A48B886435}" name="Delivery Note No." dataDxfId="160"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" name="Receiving Dock" dataDxfId="159"/>
-    <tableColumn id="27" xr3:uid="{C970C051-0950-4A04-BC06-F42CE88CB783}" name="Received By" dataDxfId="158"/>
+    <tableColumn id="21" xr3:uid="{76F9E9A1-1F34-4FAD-9BFD-02A48B886435}" name="Delivery Note No." dataDxfId="164"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" name="Receiving Dock" dataDxfId="163"/>
+    <tableColumn id="27" xr3:uid="{C970C051-0950-4A04-BC06-F42CE88CB783}" name="Received By" dataDxfId="162"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="Received Qty"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" name="Accepted Qty"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" name="Rejected Qty" dataDxfId="157">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" name="Rejected Qty" dataDxfId="161">
       <calculatedColumnFormula>tbl_GoodsReceipt[[#This Row],[Received Qty]]-tbl_GoodsReceipt[[#This Row],[Accepted Qty]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" name="Inspection Result"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0400-000011000000}" name="Rejection Reason"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" name="Batch/Lot Number"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0400-000016000000}" name="Received Variance" dataDxfId="156">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0400-000016000000}" name="Received Variance" dataDxfId="160">
       <calculatedColumnFormula>tbl_GoodsReceipt[[#This Row],[Received Qty]]-tbl_GoodsReceipt[[#This Row],[Order Qty]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0400-000017000000}" name="Received Variance %">
       <calculatedColumnFormula>IFERROR(tbl_GoodsReceipt[[#This Row],[Received Variance]]/tbl_GoodsReceipt[[#This Row],[Order Qty]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{9903FC18-7740-482D-9ABE-94B8CD52CA29}" name="Delivery Status" dataDxfId="155">
+    <tableColumn id="28" xr3:uid="{9903FC18-7740-482D-9ABE-94B8CD52CA29}" name="Delivery Status" dataDxfId="159">
       <calculatedColumnFormula>IF(tbl_GoodsReceipt[[#This Row],[GR Date]]&lt;=tbl_GoodsReceipt[[#This Row],[Expected Delivery Date]],"On-time","Late")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" name="Remarks"/>
@@ -5475,50 +5561,50 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Put Away Number"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Put Away Line"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Put Away Date"/>
-    <tableColumn id="9" xr3:uid="{3D1409EE-9BE5-4C77-8E8C-75FBB533A1BA}" name="GR Date" dataDxfId="154">
+    <tableColumn id="9" xr3:uid="{3D1409EE-9BE5-4C77-8E8C-75FBB533A1BA}" name="GR Date" dataDxfId="158">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="GR Number"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="GR Line" dataDxfId="153"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="GR Line Key (Helper)" dataDxfId="152">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="GR Line" dataDxfId="157"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="GR Line Key (Helper)" dataDxfId="156">
       <calculatedColumnFormula>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Material Code">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Material Description" dataDxfId="151">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Material Description" dataDxfId="155">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{17CC66FF-3B10-4724-A531-9ABD3C5CB8D1}" name="Batch/Lot Number" dataDxfId="150">
+    <tableColumn id="23" xr3:uid="{17CC66FF-3B10-4724-A531-9ABD3C5CB8D1}" name="Batch/Lot Number" dataDxfId="154">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="Accepted Qty">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{28CCFCA5-F3BC-430A-80E6-5C20D5AAAE8F}" name="Purchase UoM" dataDxfId="149">
+    <tableColumn id="17" xr3:uid="{28CCFCA5-F3BC-430A-80E6-5C20D5AAAE8F}" name="Purchase UoM" dataDxfId="153">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{0A641E53-0249-44B9-9E19-52E853A7C026}" name="Put Away Qty" dataDxfId="148"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="Base UoM" dataDxfId="147">
+    <tableColumn id="16" xr3:uid="{0A641E53-0249-44B9-9E19-52E853A7C026}" name="Put Away Qty" dataDxfId="152"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="Base UoM" dataDxfId="151">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="From Location" dataDxfId="146">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="From Location" dataDxfId="150">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E1EA826-7DDD-4C65-AB2E-9676F8A827A7}" name="Suggested Storage Location (Ref)" dataDxfId="145">
+    <tableColumn id="10" xr3:uid="{1E1EA826-7DDD-4C65-AB2E-9676F8A827A7}" name="Suggested Storage Location (Ref)" dataDxfId="149">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="Storage/Handling Class" dataDxfId="144">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="Storage/Handling Class" dataDxfId="148">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{BB70C6C7-B755-4415-A577-FB1FBECE67FD}" name="To Location" dataDxfId="143"/>
-    <tableColumn id="19" xr3:uid="{1445C40B-D3A5-4C1B-9654-FF2E02CAEB6A}" name="Location Storage/Handling Requirement" dataDxfId="142">
+    <tableColumn id="24" xr3:uid="{BB70C6C7-B755-4415-A577-FB1FBECE67FD}" name="To Location" dataDxfId="147"/>
+    <tableColumn id="19" xr3:uid="{1445C40B-D3A5-4C1B-9654-FF2E02CAEB6A}" name="Location Storage/Handling Requirement" dataDxfId="146">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{47D4BE73-8080-42B6-985B-6CB165C06B54}" name="Location Match Check" dataDxfId="141">
+    <tableColumn id="20" xr3:uid="{47D4BE73-8080-42B6-985B-6CB165C06B54}" name="Location Match Check" dataDxfId="145">
       <calculatedColumnFormula>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0500-000012000000}" name="Put Away Status" dataDxfId="140"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0500-000012000000}" name="Put Away Status" dataDxfId="144"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0500-000015000000}" name="Remarks"/>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0500-000016000000}" name="Put-Away Line Key (Helper)">
       <calculatedColumnFormula>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</calculatedColumnFormula>
@@ -5532,12 +5618,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="tbl_MaterialRequest" displayName="tbl_MaterialRequest" ref="A3:R18">
   <autoFilter ref="A3:R18" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}"/>
   <tableColumns count="18">
-    <tableColumn id="20" xr3:uid="{B9BDAC6D-879A-470A-ABB4-87ED00CCA6F0}" name="Request Number" totalsRowLabel="Total" dataDxfId="139" totalsRowDxfId="138"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Request Line" dataDxfId="137" totalsRowDxfId="136"/>
+    <tableColumn id="20" xr3:uid="{B9BDAC6D-879A-470A-ABB4-87ED00CCA6F0}" name="Request Number" totalsRowLabel="Total" dataDxfId="143" totalsRowDxfId="142"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Request Line" dataDxfId="141" totalsRowDxfId="140"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Request Date"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="Required Date" dataDxfId="135" totalsRowDxfId="134"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="Required Date" dataDxfId="139" totalsRowDxfId="138"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Requesting Department"/>
-    <tableColumn id="11" xr3:uid="{831BCE6C-DEE7-4065-962F-97D9A2507CC7}" name="Requester" dataDxfId="133" totalsRowDxfId="132"/>
+    <tableColumn id="11" xr3:uid="{831BCE6C-DEE7-4065-962F-97D9A2507CC7}" name="Requester" dataDxfId="137" totalsRowDxfId="136"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Material Code"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Material Description"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="Base UoM">
@@ -5545,18 +5631,18 @@
     </tableColumn>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="Quantity Requested"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="Request Priority"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="Available Stock (Ref)" dataDxfId="131">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="Available Stock (Ref)" dataDxfId="135">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],'10_Stock_Card'!F4:F32,'10_Stock_Card'!M4:M32,"",0,-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="Stock Sufficiency Check" dataDxfId="130">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="Stock Sufficiency Check" dataDxfId="134">
       <calculatedColumnFormula>IF(L4&gt;=J4,"Sufficient","Insufficient - Review")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{74FAE01D-9255-4B75-B167-77ECC7DC5BAF}" name="Approval Status" dataDxfId="129" totalsRowDxfId="128"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="Total Issued (Ref)" dataDxfId="127" totalsRowDxfId="126">
+    <tableColumn id="18" xr3:uid="{74FAE01D-9255-4B75-B167-77ECC7DC5BAF}" name="Approval Status" dataDxfId="133" totalsRowDxfId="132"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="Total Issued (Ref)" dataDxfId="131" totalsRowDxfId="130">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Request Line Key (Helper)]],tbl_GoodsIssue[MR],tbl_GoodsIssue[Quantity Issued]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" name="Request Status" dataDxfId="125" totalsRowDxfId="124"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" name="Remarks" dataDxfId="123" totalsRowDxfId="122"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" name="Request Status" dataDxfId="129" totalsRowDxfId="128"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" name="Remarks" dataDxfId="127" totalsRowDxfId="126"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" name="Request Line Key (Helper)" totalsRowFunction="count">
       <calculatedColumnFormula>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</calculatedColumnFormula>
     </tableColumn>
@@ -5577,35 +5663,35 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Request Line Key (Helper)">
       <calculatedColumnFormula>tbl_PickingList[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList[[#This Row],[Request Line]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Material Code" dataDxfId="121">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Material Code" dataDxfId="125">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Request Line Key (Helper)]],tbl_MaterialRequest[Request Line Key (Helper)],tbl_MaterialRequest[Material Code])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="Material Description" dataDxfId="120">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="Material Description" dataDxfId="124">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Request Line Key (Helper)]],tbl_MaterialRequest[Request Line Key (Helper)],tbl_MaterialRequest[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{C9E3CB77-E7C0-4337-8D57-40323596F0A3}" name="Base UoM" dataDxfId="119">
+    <tableColumn id="21" xr3:uid="{C9E3CB77-E7C0-4337-8D57-40323596F0A3}" name="Base UoM" dataDxfId="123">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Request Line Key (Helper)]],tbl_MaterialRequest[Request Line Key (Helper)],tbl_MaterialRequest[Base UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="Requesting Department (Ref)" dataDxfId="118">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="Requesting Department (Ref)" dataDxfId="122">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Request Line Key (Helper)]],tbl_MaterialRequest[Request Line Key (Helper)],tbl_MaterialRequest[Requesting Department])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="Request Priority (Ref)" dataDxfId="117">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="Request Priority (Ref)" dataDxfId="121">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Request Line Key (Helper)]],tbl_MaterialRequest[Request Line Key (Helper)],tbl_MaterialRequest[Request Priority])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="Quantity Requested (Ref)" dataDxfId="116">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="Quantity Requested (Ref)" dataDxfId="120">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Request Line Key (Helper)]],tbl_MaterialRequest[Request Line Key (Helper)],tbl_MaterialRequest[Quantity Requested])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="Pick Location " dataDxfId="115">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="Pick Location " dataDxfId="119">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Material Code]],tbl_PutAway[Material Code],tbl_PutAway[To Location])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0700-00000E000000}" name="Available Stock" dataDxfId="114">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0700-00000E000000}" name="Available Stock" dataDxfId="118">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Material Code]],'10_Stock_Card'!F4:F32,'10_Stock_Card'!M4:M32,"",0,-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="Quantity Picked" dataDxfId="113"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0700-000011000000}" name="Pick Status" dataDxfId="112">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="Quantity Picked" dataDxfId="117"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0700-000011000000}" name="Pick Status" dataDxfId="116">
       <calculatedColumnFormula>IF(tbl_PickingList[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList[[#This Row],[Quantity Picked]]&lt;tbl_PickingList[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{73D8D924-0876-4F34-9DBA-39EA7F81708E}" name="Picker" dataDxfId="111"/>
+    <tableColumn id="25" xr3:uid="{73D8D924-0876-4F34-9DBA-39EA7F81708E}" name="Picker" dataDxfId="115"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0700-000013000000}" name="Remarks"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0700-000014000000}" name="Pick Line Key (Helper)">
       <calculatedColumnFormula>tbl_PickingList[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList[[#This Row],[Pick Line]]</calculatedColumnFormula>
@@ -5624,13 +5710,13 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="GI Date"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Pick Number"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="Pick Line"/>
-    <tableColumn id="19" xr3:uid="{E93C14AF-94CF-4F14-81CC-82A7578004AD}" name="Request Number" dataDxfId="110">
+    <tableColumn id="19" xr3:uid="{E93C14AF-94CF-4F14-81CC-82A7578004AD}" name="Request Number" dataDxfId="114">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],tbl_PickingList[Pick Line Key (Helper)],tbl_PickingList[Request Number])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{38A75A8A-6A06-4489-86DF-2EE0CE3971EF}" name="Request Line" dataDxfId="109">
+    <tableColumn id="20" xr3:uid="{38A75A8A-6A06-4489-86DF-2EE0CE3971EF}" name="Request Line" dataDxfId="113">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],tbl_PickingList[Pick Line Key (Helper)],tbl_PickingList[Request Line])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Pick Line Key (Helper)" dataDxfId="108">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Pick Line Key (Helper)" dataDxfId="112">
       <calculatedColumnFormula>D4&amp;"-"&amp;E4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="Material Code">
@@ -5639,32 +5725,32 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="Material Description">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="Base UoM" dataDxfId="107">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="Base UoM" dataDxfId="111">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="Issuing Location (Ref)" dataDxfId="106">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="Issuing Location (Ref)" dataDxfId="110">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],tbl_PickingList[Pick Line Key (Helper)],tbl_PickingList[[Pick Location ]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0800-00000B000000}" name="Requesting Department (Ref)" dataDxfId="105">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0800-00000B000000}" name="Requesting Department (Ref)" dataDxfId="109">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],tbl_PickingList[Pick Line Key (Helper)],tbl_PickingList[Requesting Department (Ref)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0800-00000C000000}" name="Quantity Picked (Ref)" dataDxfId="104">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0800-00000C000000}" name="Quantity Picked (Ref)" dataDxfId="108">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],tbl_PickingList[Pick Line Key (Helper)],tbl_PickingList[Quantity Picked])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0800-00000D000000}" name="Quantity Issued"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0800-00000E000000}" name="Issue Variance" dataDxfId="103">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0800-00000E000000}" name="Issue Variance" dataDxfId="107">
       <calculatedColumnFormula>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{604A2A6F-C4DD-4034-9B7B-D193996479E5}" name="Issue Status" dataDxfId="102">
+    <tableColumn id="15" xr3:uid="{604A2A6F-C4DD-4034-9B7B-D193996479E5}" name="Issue Status" dataDxfId="106">
       <calculatedColumnFormula>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{90D76B52-520C-4D83-81A3-B6E72FB0F149}" name="Issued By" dataDxfId="101"/>
-    <tableColumn id="22" xr3:uid="{76096732-D4A3-4A12-8DD0-430477B5B0BF}" name="Received By" dataDxfId="100"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0800-000010000000}" name="Remarks" dataDxfId="99"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0800-000011000000}" name="GI Line Key (Helper)" dataDxfId="98">
+    <tableColumn id="21" xr3:uid="{90D76B52-520C-4D83-81A3-B6E72FB0F149}" name="Issued By" dataDxfId="105"/>
+    <tableColumn id="22" xr3:uid="{76096732-D4A3-4A12-8DD0-430477B5B0BF}" name="Received By" dataDxfId="104"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0800-000010000000}" name="Remarks" dataDxfId="103"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0800-000011000000}" name="GI Line Key (Helper)" dataDxfId="102">
       <calculatedColumnFormula>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{21F1F36F-2396-482F-BFCE-12F60C905BC9}" name="MR" dataDxfId="97">
+    <tableColumn id="23" xr3:uid="{21F1F36F-2396-482F-BFCE-12F60C905BC9}" name="MR" dataDxfId="101">
       <calculatedColumnFormula>tbl_GoodsIssue[[#This Row],[Request Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[Request Line]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6014,10 +6100,10 @@
         <v>24</v>
       </c>
       <c r="K5" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L5" s="3">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="M5" s="3">
         <v>21</v>
@@ -6059,10 +6145,10 @@
         <v>19</v>
       </c>
       <c r="K6" s="3">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="L6" s="3">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="M6" s="3">
         <v>7</v>
@@ -6149,7 +6235,7 @@
         <v>35</v>
       </c>
       <c r="K8" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L8" s="3">
         <v>200</v>
@@ -6284,10 +6370,10 @@
         <v>19</v>
       </c>
       <c r="K11" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L11" s="3">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="M11" s="3">
         <v>12</v>
@@ -6419,10 +6505,10 @@
         <v>24</v>
       </c>
       <c r="K14" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="L14" s="3">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="M14" s="3">
         <v>45</v>
@@ -6464,7 +6550,7 @@
         <v>24</v>
       </c>
       <c r="K15" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L15" s="3">
         <v>120</v>
@@ -6599,7 +6685,7 @@
         <v>24</v>
       </c>
       <c r="K18" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L18" s="3">
         <v>50</v>
@@ -6644,7 +6730,7 @@
         <v>19</v>
       </c>
       <c r="K19" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L19" s="3">
         <v>200</v>
@@ -6689,10 +6775,10 @@
         <v>24</v>
       </c>
       <c r="K20" s="3">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="L20" s="3">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>25</v>
@@ -6779,10 +6865,10 @@
         <v>19</v>
       </c>
       <c r="K22" s="3">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L22" s="3">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="M22" s="3">
         <v>9</v>
@@ -6824,10 +6910,10 @@
         <v>24</v>
       </c>
       <c r="K23" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L23" s="3">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="M23" s="3">
         <v>40</v>
@@ -6863,35 +6949,43 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A31:E53">
-    <cfRule type="expression" dxfId="82" priority="103">
+    <cfRule type="expression" dxfId="86" priority="105">
       <formula>$E31="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="104">
+    <cfRule type="expression" dxfId="85" priority="106">
       <formula>#REF!="Critical Spare"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:O23">
-    <cfRule type="expression" dxfId="80" priority="28">
+  <conditionalFormatting sqref="A4:J23 M4:O23">
+    <cfRule type="expression" dxfId="84" priority="30">
       <formula>$N4="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="29">
+    <cfRule type="expression" dxfId="83" priority="31">
       <formula>$I4="Critical Spare"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:O30 A54:O498">
-    <cfRule type="expression" dxfId="78" priority="20">
+    <cfRule type="expression" dxfId="82" priority="22">
       <formula>$O24="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="21">
+    <cfRule type="expression" dxfId="81" priority="23">
       <formula>$I24="Critical Spare"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F23">
-    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23">
-    <cfRule type="containsText" dxfId="75" priority="1" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="79" priority="3" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",H4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4:L23">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$N4="Inactive"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$I4="Critical Spare"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="8">
@@ -8908,33 +9002,33 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="A33:A39 A41:A518">
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="22" priority="2">
       <formula>$A33="Receipt"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="21" priority="3">
       <formula>$A33="Issue"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:B32">
-    <cfRule type="expression" dxfId="16" priority="5">
+    <cfRule type="expression" dxfId="20" priority="5">
       <formula>$B4="Goods Receipt"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="6">
+    <cfRule type="expression" dxfId="19" priority="6">
       <formula>$B4="Goods Issue"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L32">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>$L4&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L33:L518">
-    <cfRule type="expression" dxfId="13" priority="4">
+    <cfRule type="expression" dxfId="17" priority="4">
       <formula>$L33&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:M32">
-    <cfRule type="expression" dxfId="12" priority="7">
+    <cfRule type="expression" dxfId="16" priority="7">
       <formula>$M4&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9646,50 +9740,50 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A24:A47">
-    <cfRule type="expression" dxfId="11" priority="117">
+    <cfRule type="expression" dxfId="15" priority="117">
       <formula>#REF!="Shortage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="118">
+    <cfRule type="expression" dxfId="14" priority="118">
       <formula>#REF!="Overage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="119">
+    <cfRule type="expression" dxfId="13" priority="119">
       <formula>#REF!="Match"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:D47">
-    <cfRule type="expression" dxfId="8" priority="121">
+    <cfRule type="expression" dxfId="12" priority="121">
       <formula>$C24="Under Investigation"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:O23 M48:O504">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>$M12="Shortage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="10" priority="4">
       <formula>$M12="Overage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>$M12="Match"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:P11">
-    <cfRule type="expression" dxfId="4" priority="110">
+    <cfRule type="expression" dxfId="8" priority="110">
       <formula>$N4="Shortage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="111">
+    <cfRule type="expression" dxfId="7" priority="111">
       <formula>$N4="Overage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="112">
+    <cfRule type="expression" dxfId="6" priority="112">
       <formula>$N4="Match"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12:R23 Q48:R504">
-    <cfRule type="expression" dxfId="1" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$Q12="Under Investigation"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4:R11 T4:T11">
-    <cfRule type="expression" dxfId="0" priority="113">
+    <cfRule type="expression" dxfId="4" priority="113">
       <formula>$R4="Under Investigation"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10248,15 +10342,15 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A4:I13">
-    <cfRule type="expression" dxfId="74" priority="37">
+    <cfRule type="expression" dxfId="78" priority="37">
       <formula>$I4="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="38">
+    <cfRule type="expression" dxfId="77" priority="38">
       <formula>$H4="Preferred"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H21">
-    <cfRule type="expression" dxfId="72" priority="7">
+    <cfRule type="expression" dxfId="76" priority="7">
       <formula>$H14="Under Review"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11202,36 +11296,36 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A29:G36 A46:B55 A56:G512">
-    <cfRule type="expression" dxfId="71" priority="2">
+    <cfRule type="expression" dxfId="75" priority="2">
       <formula>$G29="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="3">
+    <cfRule type="expression" dxfId="74" priority="3">
       <formula>$D29="Hazardous"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:H15 A16:F17 H16:H17 A18:H28">
-    <cfRule type="expression" dxfId="69" priority="41">
+    <cfRule type="expression" dxfId="73" priority="41">
       <formula>$H4="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="42">
+    <cfRule type="expression" dxfId="72" priority="42">
       <formula>$E4="Hazardous"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29:E36 E56:E512">
-    <cfRule type="expression" dxfId="67" priority="4">
+    <cfRule type="expression" dxfId="71" priority="4">
       <formula>$E29="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F28">
-    <cfRule type="expression" dxfId="66" priority="46">
+    <cfRule type="expression" dxfId="70" priority="46">
       <formula>$F4="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G16">
-    <cfRule type="expression" dxfId="65" priority="105">
+    <cfRule type="expression" dxfId="69" priority="105">
       <formula>$H17="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="106">
+    <cfRule type="expression" dxfId="68" priority="106">
       <formula>$E17="Hazardous"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13102,53 +13196,53 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="C33:C79">
-    <cfRule type="expression" dxfId="63" priority="127">
+    <cfRule type="expression" dxfId="67" priority="127">
       <formula>$C33="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33:G79">
-    <cfRule type="expression" dxfId="62" priority="131">
+    <cfRule type="expression" dxfId="66" priority="131">
       <formula>$G33="Cancelled"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="132">
+    <cfRule type="expression" dxfId="65" priority="132">
       <formula>$G33="Closed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="133">
+    <cfRule type="expression" dxfId="64" priority="133">
       <formula>$G33="Open"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L26 L28:L29">
-    <cfRule type="expression" dxfId="59" priority="56">
+    <cfRule type="expression" dxfId="63" priority="56">
       <formula>$L4="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N30:N32 N80:N515">
-    <cfRule type="expression" dxfId="58" priority="3">
+    <cfRule type="expression" dxfId="62" priority="3">
       <formula>$N30="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q26 Q28:Q29">
-    <cfRule type="expression" dxfId="57" priority="1">
+    <cfRule type="expression" dxfId="61" priority="1">
       <formula>$Q4="Partial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="64">
+    <cfRule type="expression" dxfId="60" priority="64">
       <formula>$Q4="Cancelled"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="65">
+    <cfRule type="expression" dxfId="59" priority="65">
       <formula>$Q4="Closed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="66">
+    <cfRule type="expression" dxfId="58" priority="66">
       <formula>$Q4="Open"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R30:R32 R80:R515">
-    <cfRule type="expression" dxfId="53" priority="4">
+    <cfRule type="expression" dxfId="57" priority="4">
       <formula>$R30="Cancelled"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="5">
+    <cfRule type="expression" dxfId="56" priority="5">
       <formula>$R30="Closed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="6">
+    <cfRule type="expression" dxfId="55" priority="6">
       <formula>$R30="Open"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15383,31 +15477,31 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="K24:K35">
-    <cfRule type="expression" dxfId="50" priority="124">
+    <cfRule type="expression" dxfId="54" priority="124">
       <formula>$K24="Fully Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="125">
+    <cfRule type="expression" dxfId="53" priority="125">
       <formula>$K24="Partially Accepted"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S22:S23 S36:S512">
-    <cfRule type="expression" dxfId="48" priority="6">
+    <cfRule type="expression" dxfId="52" priority="6">
       <formula>$S22="Fully Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="7">
+    <cfRule type="expression" dxfId="51" priority="7">
       <formula>$S22="Partially Accepted"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4:U21">
-    <cfRule type="expression" dxfId="46" priority="61">
+    <cfRule type="expression" dxfId="50" priority="61">
       <formula>$U4="Fully Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="62">
+    <cfRule type="expression" dxfId="49" priority="62">
       <formula>$U4="Partially Accepted"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:Z21">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>$Z4="Late"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17236,26 +17330,26 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="Q22:Q513">
-    <cfRule type="expression" dxfId="43" priority="5">
+    <cfRule type="expression" dxfId="47" priority="5">
       <formula>$Q22="Mismatch - Review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4:R20">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:T20">
-    <cfRule type="expression" dxfId="41" priority="2">
+    <cfRule type="expression" dxfId="45" priority="2">
       <formula>$T4="Mismatch - Review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4:U20">
-    <cfRule type="expression" dxfId="40" priority="3">
+    <cfRule type="expression" dxfId="44" priority="3">
       <formula>$U4="Partial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="74">
+    <cfRule type="expression" dxfId="43" priority="74">
       <formula>$U4="Exception - Needs Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="75">
+    <cfRule type="expression" dxfId="42" priority="75">
       <formula>$U4="Completed"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18338,28 +18432,28 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="I19:I507">
-    <cfRule type="expression" dxfId="37" priority="2">
+    <cfRule type="expression" dxfId="41" priority="2">
       <formula>$I19="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K18">
-    <cfRule type="expression" dxfId="36" priority="83">
+    <cfRule type="expression" dxfId="40" priority="83">
       <formula>$K4="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N18">
-    <cfRule type="expression" dxfId="35" priority="80">
+    <cfRule type="expression" dxfId="39" priority="80">
       <formula>$M4="Insufficient - Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="81">
+    <cfRule type="expression" dxfId="38" priority="81">
       <formula>$M4="Sufficient"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:N507">
-    <cfRule type="expression" dxfId="33" priority="3">
+    <cfRule type="expression" dxfId="37" priority="3">
       <formula>$N19="Insufficient - Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="4">
+    <cfRule type="expression" dxfId="36" priority="4">
       <formula>$N19="Sufficient"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19361,31 +19455,31 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="K4:K18 K80:K507">
-    <cfRule type="expression" dxfId="31" priority="2">
+    <cfRule type="expression" dxfId="35" priority="2">
       <formula>$K4="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:P15">
-    <cfRule type="expression" dxfId="30" priority="88">
+    <cfRule type="expression" dxfId="34" priority="88">
       <formula>$P4="Fully Picked"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:Q15">
-    <cfRule type="expression" dxfId="29" priority="87">
+    <cfRule type="expression" dxfId="33" priority="87">
       <formula>$P4="Partially Picked"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="89">
+    <cfRule type="expression" dxfId="32" priority="89">
       <formula>$P4="Not Picked"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q16:Q17 Q80:Q507">
-    <cfRule type="expression" dxfId="27" priority="4">
+    <cfRule type="expression" dxfId="31" priority="4">
       <formula>$Q16="Partially Picked"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="5">
+    <cfRule type="expression" dxfId="30" priority="5">
       <formula>$Q16="Fully Picked"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="6">
+    <cfRule type="expression" dxfId="29" priority="6">
       <formula>$Q16="Not Picked"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20687,32 +20781,32 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="P4:Q15">
-    <cfRule type="expression" dxfId="24" priority="92">
+    <cfRule type="expression" dxfId="28" priority="92">
       <formula>$P4&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q15">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>$Q4="Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:S15">
-    <cfRule type="expression" dxfId="22" priority="95">
+    <cfRule type="expression" dxfId="26" priority="95">
       <formula>#REF!&lt;&gt;"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q16:S16 O17:Q28 Q29:S507">
-    <cfRule type="expression" dxfId="21" priority="96">
+    <cfRule type="expression" dxfId="25" priority="96">
       <formula>#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R17:R28">
-    <cfRule type="expression" dxfId="20" priority="100">
+    <cfRule type="expression" dxfId="24" priority="100">
       <formula>$R17&lt;&gt;"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T16:U16 T29:U507">
-    <cfRule type="expression" dxfId="19" priority="4">
+    <cfRule type="expression" dxfId="23" priority="4">
       <formula>$T16&lt;&gt;"N/A"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Warehouse_Operations_Simulation.xlsx
+++ b/Warehouse_Operations_Simulation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Upgrade skill\1. Excel - Data Analytics\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700275E2-3C0F-4E86-A8FD-1C0B2EE12777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042D5C3B-5F50-4CC4-8A9F-D0516E45FEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2064,92 +2064,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="203">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFB7B7B7"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFB7B7B7"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFB7B7B7"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFB7B7B7"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFB7B7B7"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFB7B7B7"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFB7B7B7"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFB7B7B7"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <i/>
@@ -2822,6 +2736,20 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -5075,6 +5003,78 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB7B7B7"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB7B7B7"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB7B7B7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB7B7B7"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FFB7B7B7"/>
@@ -5347,11 +5347,11 @@
     <tableColumn id="5" xr3:uid="{01500A3B-77EE-4BAE-BC67-664F09E22186}" name="ABC Classification" dataDxfId="197"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Criticality Flag"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Storage/Handling Class"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Min Stock Level" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Max Stock Level" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Min Stock Level" dataDxfId="196"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Max Stock Level" dataDxfId="195"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Lead Time (Days)"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Status"/>
-    <tableColumn id="22" xr3:uid="{BC7C3BEF-CB66-4A5F-9E71-E29F8E60C070}" name="Remarks" dataDxfId="196"/>
+    <tableColumn id="22" xr3:uid="{BC7C3BEF-CB66-4A5F-9E71-E29F8E60C070}" name="Remarks" dataDxfId="194"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5365,36 +5365,36 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Count Line"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Count Date"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="Material Code"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="Material Description" dataDxfId="100">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="Material Description" dataDxfId="98">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_CycleCount[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{42D72B1C-0469-448F-89C5-AE97F1EFA4A3}" name="ABC Classification" dataDxfId="99">
+    <tableColumn id="20" xr3:uid="{42D72B1C-0469-448F-89C5-AE97F1EFA4A3}" name="ABC Classification" dataDxfId="97">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_CycleCount[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[ABC Classification])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="Count Location (Ref)" dataDxfId="98"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="System Qty (Ref)" dataDxfId="97">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="Count Location (Ref)" dataDxfId="96"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="System Qty (Ref)" dataDxfId="95">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_CycleCount[[#This Row],[Material Code]],'10_Stock_Card'!F4:F32,'10_Stock_Card'!M4:M32,"",,-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0A00-00000A000000}" name="Physical Count" dataDxfId="96"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0A00-00000B000000}" name="Variance (Qty)" dataDxfId="95">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0A00-00000A000000}" name="Physical Count" dataDxfId="94"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0A00-00000B000000}" name="Variance (Qty)" dataDxfId="93">
       <calculatedColumnFormula>tbl_CycleCount[[#This Row],[Physical Count]]-tbl_CycleCount[[#This Row],[System Qty (Ref)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0A00-00000C000000}" name="Variance %" dataDxfId="94">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0A00-00000C000000}" name="Variance %" dataDxfId="92">
       <calculatedColumnFormula>IFERROR(tbl_CycleCount[[#This Row],[Variance (Qty)]]/tbl_CycleCount[[#This Row],[System Qty (Ref)]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0A00-00000D000000}" name="Unit Cost (Ref)" dataDxfId="93">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0A00-00000D000000}" name="Unit Cost (Ref)" dataDxfId="91">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_CycleCount[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Standard Cost (per Base UoM)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0A00-00000E000000}" name="Variance Value" dataDxfId="92">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0A00-00000E000000}" name="Variance Value" dataDxfId="90">
       <calculatedColumnFormula>tbl_CycleCount[[#This Row],[Variance (Qty)]]*tbl_CycleCount[[#This Row],[Unit Cost (Ref)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0A00-00000F000000}" name="Count Result" dataDxfId="91"/>
-    <tableColumn id="7" xr3:uid="{19FA728F-5901-4A45-82C7-A24BD8CD672D}" name="Count By" dataDxfId="90"/>
-    <tableColumn id="6" xr3:uid="{40535110-8F23-4B6C-8557-AF648D9A2B41}" name="Verified By" dataDxfId="89"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0A00-000010000000}" name="Root Cause" dataDxfId="88"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0A00-00000F000000}" name="Count Result" dataDxfId="89"/>
+    <tableColumn id="7" xr3:uid="{19FA728F-5901-4A45-82C7-A24BD8CD672D}" name="Count By" dataDxfId="88"/>
+    <tableColumn id="6" xr3:uid="{40535110-8F23-4B6C-8557-AF648D9A2B41}" name="Verified By" dataDxfId="87"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0A00-000010000000}" name="Root Cause" dataDxfId="86"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0A00-000011000000}" name="Adjustment Status"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0A00-000012000000}" name="Remarks"/>
-    <tableColumn id="19" xr3:uid="{2718145A-3CE3-42EB-A2A9-5B850CE78E6D}" name="Count Line Key (Helper)" dataDxfId="87">
+    <tableColumn id="19" xr3:uid="{2718145A-3CE3-42EB-A2A9-5B850CE78E6D}" name="Count Line Key (Helper)" dataDxfId="85">
       <calculatedColumnFormula>tbl_CycleCount[[#This Row],[Count Number]]&amp;"-"&amp;tbl_CycleCount[[#This Row],[Count Line]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5427,7 +5427,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Location Code"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Location Description"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Zone"/>
-    <tableColumn id="8" xr3:uid="{276A2345-C837-4FC6-B4E0-FF35EB523268}" name="Location Type" dataDxfId="195"/>
+    <tableColumn id="8" xr3:uid="{276A2345-C837-4FC6-B4E0-FF35EB523268}" name="Location Type" dataDxfId="193"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Storage/Handling Requirement"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Pickable Flag"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Capacity (Max Qty)"/>
@@ -5448,37 +5448,37 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="PO Line"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="PO Date"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Supplier Code"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Supplier Name" dataDxfId="194">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Supplier Name" dataDxfId="192">
       <calculatedColumnFormula>VLOOKUP(tbl_PurchaseOrder[[#This Row],[Supplier Code]],tbl_MasterSupplier[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Material Code"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Material Description" dataDxfId="193">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Material Description" dataDxfId="191">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PurchaseOrder[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Purchase UoM" dataDxfId="192"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Ordered Qty" dataDxfId="191" totalsRowDxfId="190"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Unit Price" dataDxfId="189" totalsRowDxfId="188"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Line Total" dataDxfId="187" totalsRowDxfId="186">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Purchase UoM" dataDxfId="190"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Ordered Qty" dataDxfId="189" totalsRowDxfId="188"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Unit Price" dataDxfId="187" totalsRowDxfId="186"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Line Total" dataDxfId="185" totalsRowDxfId="184">
       <calculatedColumnFormula>tbl_PurchaseOrder[[#This Row],[Ordered Qty]]*J4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="Order Priority" dataDxfId="185" totalsRowDxfId="184"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="Order Priority" dataDxfId="183" totalsRowDxfId="182"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="Lead Time (Days)">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PurchaseOrder[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Lead Time (Days)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="Expected Delivery Date" dataDxfId="183">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="Expected Delivery Date" dataDxfId="181">
       <calculatedColumnFormula>tbl_PurchaseOrder[[#This Row],[PO Date]]+tbl_PurchaseOrder[[#This Row],[Lead Time (Days)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{09E53041-1B48-4B81-BCF8-287332AE53AE}" name="Received Qty" dataDxfId="182" totalsRowDxfId="181">
+    <tableColumn id="13" xr3:uid="{09E53041-1B48-4B81-BCF8-287332AE53AE}" name="Received Qty" dataDxfId="180" totalsRowDxfId="179">
       <calculatedColumnFormula>SUMIFS(tbl_GoodsReceipt[Received Qty],tbl_GoodsReceipt[PO Line Key (Helper)],tbl_PurchaseOrder[[#This Row],[PO Line Key (Helper)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{123695AE-1CB2-4070-BEE2-29FE092ACFA7}" name="Outstanding Qty" dataDxfId="180" totalsRowDxfId="179">
+    <tableColumn id="14" xr3:uid="{123695AE-1CB2-4070-BEE2-29FE092ACFA7}" name="Outstanding Qty" dataDxfId="178" totalsRowDxfId="177">
       <calculatedColumnFormula>IFERROR(tbl_PurchaseOrder[[#This Row],[Received Qty]]-tbl_PurchaseOrder[[#This Row],[Ordered Qty]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="PO Status" dataDxfId="178">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="PO Status" dataDxfId="176">
       <calculatedColumnFormula>IF(tbl_PurchaseOrder[[#This Row],[Received Qty]]=0,"Open",IF(tbl_PurchaseOrder[[#This Row],[Received Qty]]&lt;tbl_PurchaseOrder[[#This Row],[Ordered Qty]],"Partial", "Closed"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Remarks" dataDxfId="177"/>
-    <tableColumn id="19" xr3:uid="{195CE6D1-9D3F-4D81-9DE2-B82EEBF35742}" name="PO Line Key (Helper)" dataDxfId="176" totalsRowDxfId="175">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Remarks" dataDxfId="175"/>
+    <tableColumn id="19" xr3:uid="{195CE6D1-9D3F-4D81-9DE2-B82EEBF35742}" name="PO Line Key (Helper)" dataDxfId="174" totalsRowDxfId="173">
       <calculatedColumnFormula>tbl_PurchaseOrder[[#This Row],[PO Number]]&amp;"-"&amp;tbl_PurchaseOrder[[#This Row],[PO Line]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5497,52 +5497,52 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="GR Line"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="GR Date"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="PO Number"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="PO Line" dataDxfId="174"/>
-    <tableColumn id="29" xr3:uid="{32467FAF-3D7D-4CA5-9707-3FB4E795D1FA}" name="PO Line Key (Helper)" dataDxfId="173">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="PO Line" dataDxfId="172"/>
+    <tableColumn id="29" xr3:uid="{32467FAF-3D7D-4CA5-9707-3FB4E795D1FA}" name="PO Line Key (Helper)" dataDxfId="171">
       <calculatedColumnFormula>tbl_GoodsReceipt[[#This Row],[PO Number]]&amp;"-"&amp;tbl_GoodsReceipt[[#This Row],[PO Line]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E8DA1EE4-E020-4801-93F4-A35A7E1B2656}" name="Supplier Code" dataDxfId="172">
+    <tableColumn id="6" xr3:uid="{E8DA1EE4-E020-4801-93F4-A35A7E1B2656}" name="Supplier Code" dataDxfId="170">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Supplier Code])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Supplier Name" dataDxfId="171">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Supplier Name" dataDxfId="169">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[Supplier Code]],tbl_MasterSupplier[Supplier Code],tbl_MasterSupplier[Supplier Name])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Material Code" dataDxfId="170">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Material Code" dataDxfId="168">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Material Code])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Material Description" dataDxfId="169">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Material Description" dataDxfId="167">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="Order Qty" dataDxfId="168">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="Order Qty" dataDxfId="166">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Ordered Qty])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="Purchase UoM" dataDxfId="167">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0400-00000C000000}" name="Purchase UoM" dataDxfId="165">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Purchase UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="Unit Price" dataDxfId="166">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="Unit Price" dataDxfId="164">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Unit Price])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" name="Expected Delivery Date" dataDxfId="165">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" name="Expected Delivery Date" dataDxfId="163">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Expected Delivery Date])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{76F9E9A1-1F34-4FAD-9BFD-02A48B886435}" name="Delivery Note No." dataDxfId="164"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" name="Receiving Dock" dataDxfId="163"/>
-    <tableColumn id="27" xr3:uid="{C970C051-0950-4A04-BC06-F42CE88CB783}" name="Received By" dataDxfId="162"/>
+    <tableColumn id="21" xr3:uid="{76F9E9A1-1F34-4FAD-9BFD-02A48B886435}" name="Delivery Note No." dataDxfId="162"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" name="Receiving Dock" dataDxfId="161"/>
+    <tableColumn id="27" xr3:uid="{C970C051-0950-4A04-BC06-F42CE88CB783}" name="Received By" dataDxfId="160"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="Received Qty"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" name="Accepted Qty"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" name="Rejected Qty" dataDxfId="161">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0400-00000F000000}" name="Rejected Qty" dataDxfId="159">
       <calculatedColumnFormula>tbl_GoodsReceipt[[#This Row],[Received Qty]]-tbl_GoodsReceipt[[#This Row],[Accepted Qty]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" name="Inspection Result"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0400-000011000000}" name="Rejection Reason"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" name="Batch/Lot Number"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0400-000016000000}" name="Received Variance" dataDxfId="160">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0400-000016000000}" name="Received Variance" dataDxfId="158">
       <calculatedColumnFormula>tbl_GoodsReceipt[[#This Row],[Received Qty]]-tbl_GoodsReceipt[[#This Row],[Order Qty]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0400-000017000000}" name="Received Variance %">
       <calculatedColumnFormula>IFERROR(tbl_GoodsReceipt[[#This Row],[Received Variance]]/tbl_GoodsReceipt[[#This Row],[Order Qty]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{9903FC18-7740-482D-9ABE-94B8CD52CA29}" name="Delivery Status" dataDxfId="159">
+    <tableColumn id="28" xr3:uid="{9903FC18-7740-482D-9ABE-94B8CD52CA29}" name="Delivery Status" dataDxfId="157">
       <calculatedColumnFormula>IF(tbl_GoodsReceipt[[#This Row],[GR Date]]&lt;=tbl_GoodsReceipt[[#This Row],[Expected Delivery Date]],"On-time","Late")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" name="Remarks"/>
@@ -5561,50 +5561,50 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Put Away Number"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Put Away Line"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Put Away Date"/>
-    <tableColumn id="9" xr3:uid="{3D1409EE-9BE5-4C77-8E8C-75FBB533A1BA}" name="GR Date" dataDxfId="158">
+    <tableColumn id="9" xr3:uid="{3D1409EE-9BE5-4C77-8E8C-75FBB533A1BA}" name="GR Date" dataDxfId="156">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[GR Date])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="GR Number"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="GR Line" dataDxfId="157"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="GR Line Key (Helper)" dataDxfId="156">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="GR Line" dataDxfId="155"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="GR Line Key (Helper)" dataDxfId="154">
       <calculatedColumnFormula>tbl_PutAway[[#This Row],[GR Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[GR Line]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Material Code">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Material Code])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Material Description" dataDxfId="155">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Material Description" dataDxfId="153">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_GoodsReceipt[Material Code],tbl_GoodsReceipt[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{17CC66FF-3B10-4724-A531-9ABD3C5CB8D1}" name="Batch/Lot Number" dataDxfId="154">
+    <tableColumn id="23" xr3:uid="{17CC66FF-3B10-4724-A531-9ABD3C5CB8D1}" name="Batch/Lot Number" dataDxfId="152">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Batch/Lot Number])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="Accepted Qty">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{28CCFCA5-F3BC-430A-80E6-5C20D5AAAE8F}" name="Purchase UoM" dataDxfId="153">
+    <tableColumn id="17" xr3:uid="{28CCFCA5-F3BC-430A-80E6-5C20D5AAAE8F}" name="Purchase UoM" dataDxfId="151">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{0A641E53-0249-44B9-9E19-52E853A7C026}" name="Put Away Qty" dataDxfId="152"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="Base UoM" dataDxfId="151">
+    <tableColumn id="16" xr3:uid="{0A641E53-0249-44B9-9E19-52E853A7C026}" name="Put Away Qty" dataDxfId="150"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="Base UoM" dataDxfId="149">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="From Location" dataDxfId="150">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="From Location" dataDxfId="148">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Receiving Dock])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E1EA826-7DDD-4C65-AB2E-9676F8A827A7}" name="Suggested Storage Location (Ref)" dataDxfId="149">
+    <tableColumn id="10" xr3:uid="{1E1EA826-7DDD-4C65-AB2E-9676F8A827A7}" name="Suggested Storage Location (Ref)" dataDxfId="147">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Default Storage Location])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="Storage/Handling Class" dataDxfId="148">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="Storage/Handling Class" dataDxfId="146">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Storage/Handling Class])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{BB70C6C7-B755-4415-A577-FB1FBECE67FD}" name="To Location" dataDxfId="147"/>
-    <tableColumn id="19" xr3:uid="{1445C40B-D3A5-4C1B-9654-FF2E02CAEB6A}" name="Location Storage/Handling Requirement" dataDxfId="146">
+    <tableColumn id="24" xr3:uid="{BB70C6C7-B755-4415-A577-FB1FBECE67FD}" name="To Location" dataDxfId="145"/>
+    <tableColumn id="19" xr3:uid="{1445C40B-D3A5-4C1B-9654-FF2E02CAEB6A}" name="Location Storage/Handling Requirement" dataDxfId="144">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[To Location]],tbl_MasterLocation[Location Code],tbl_MasterLocation[Storage/Handling Requirement])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{47D4BE73-8080-42B6-985B-6CB165C06B54}" name="Location Match Check" dataDxfId="145">
+    <tableColumn id="20" xr3:uid="{47D4BE73-8080-42B6-985B-6CB165C06B54}" name="Location Match Check" dataDxfId="143">
       <calculatedColumnFormula>IF(tbl_PutAway[[#This Row],[Location Storage/Handling Requirement]]=tbl_PutAway[[#This Row],[Storage/Handling Class]],"Match","Mismatch - Review")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0500-000012000000}" name="Put Away Status" dataDxfId="144"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0500-000012000000}" name="Put Away Status" dataDxfId="142"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0500-000015000000}" name="Remarks"/>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0500-000016000000}" name="Put-Away Line Key (Helper)">
       <calculatedColumnFormula>tbl_PutAway[[#This Row],[Put Away Number]]&amp;"-"&amp;tbl_PutAway[[#This Row],[Put Away Line]]</calculatedColumnFormula>
@@ -5618,12 +5618,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="tbl_MaterialRequest" displayName="tbl_MaterialRequest" ref="A3:R18">
   <autoFilter ref="A3:R18" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}"/>
   <tableColumns count="18">
-    <tableColumn id="20" xr3:uid="{B9BDAC6D-879A-470A-ABB4-87ED00CCA6F0}" name="Request Number" totalsRowLabel="Total" dataDxfId="143" totalsRowDxfId="142"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Request Line" dataDxfId="141" totalsRowDxfId="140"/>
+    <tableColumn id="20" xr3:uid="{B9BDAC6D-879A-470A-ABB4-87ED00CCA6F0}" name="Request Number" totalsRowLabel="Total" dataDxfId="141" totalsRowDxfId="140"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Request Line" dataDxfId="139" totalsRowDxfId="138"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Request Date"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="Required Date" dataDxfId="139" totalsRowDxfId="138"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="Required Date" dataDxfId="137" totalsRowDxfId="136"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Requesting Department"/>
-    <tableColumn id="11" xr3:uid="{831BCE6C-DEE7-4065-962F-97D9A2507CC7}" name="Requester" dataDxfId="137" totalsRowDxfId="136"/>
+    <tableColumn id="11" xr3:uid="{831BCE6C-DEE7-4065-962F-97D9A2507CC7}" name="Requester" dataDxfId="135" totalsRowDxfId="134"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Material Code"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Material Description"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="Base UoM">
@@ -5631,18 +5631,18 @@
     </tableColumn>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="Quantity Requested"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="Request Priority"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="Available Stock (Ref)" dataDxfId="135">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="Available Stock (Ref)" dataDxfId="133">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],'10_Stock_Card'!F4:F32,'10_Stock_Card'!M4:M32,"",0,-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="Stock Sufficiency Check" dataDxfId="134">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="Stock Sufficiency Check" dataDxfId="132">
       <calculatedColumnFormula>IF(L4&gt;=J4,"Sufficient","Insufficient - Review")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{74FAE01D-9255-4B75-B167-77ECC7DC5BAF}" name="Approval Status" dataDxfId="133" totalsRowDxfId="132"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="Total Issued (Ref)" dataDxfId="131" totalsRowDxfId="130">
+    <tableColumn id="18" xr3:uid="{74FAE01D-9255-4B75-B167-77ECC7DC5BAF}" name="Approval Status" dataDxfId="131" totalsRowDxfId="130"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="Total Issued (Ref)" dataDxfId="129" totalsRowDxfId="128">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Request Line Key (Helper)]],tbl_GoodsIssue[MR],tbl_GoodsIssue[Quantity Issued]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" name="Request Status" dataDxfId="129" totalsRowDxfId="128"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" name="Remarks" dataDxfId="127" totalsRowDxfId="126"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" name="Request Status" dataDxfId="127" totalsRowDxfId="126"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" name="Remarks" dataDxfId="125" totalsRowDxfId="124"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" name="Request Line Key (Helper)" totalsRowFunction="count">
       <calculatedColumnFormula>tbl_MaterialRequest[[#This Row],[Request Number]]&amp;"-"&amp;tbl_MaterialRequest[[#This Row],[Request Line]]</calculatedColumnFormula>
     </tableColumn>
@@ -5663,35 +5663,35 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Request Line Key (Helper)">
       <calculatedColumnFormula>tbl_PickingList[[#This Row],[Request Number]]&amp;"-"&amp;tbl_PickingList[[#This Row],[Request Line]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Material Code" dataDxfId="125">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Material Code" dataDxfId="123">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Request Line Key (Helper)]],tbl_MaterialRequest[Request Line Key (Helper)],tbl_MaterialRequest[Material Code])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="Material Description" dataDxfId="124">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="Material Description" dataDxfId="122">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Request Line Key (Helper)]],tbl_MaterialRequest[Request Line Key (Helper)],tbl_MaterialRequest[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{C9E3CB77-E7C0-4337-8D57-40323596F0A3}" name="Base UoM" dataDxfId="123">
+    <tableColumn id="21" xr3:uid="{C9E3CB77-E7C0-4337-8D57-40323596F0A3}" name="Base UoM" dataDxfId="121">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Request Line Key (Helper)]],tbl_MaterialRequest[Request Line Key (Helper)],tbl_MaterialRequest[Base UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="Requesting Department (Ref)" dataDxfId="122">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="Requesting Department (Ref)" dataDxfId="120">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Request Line Key (Helper)]],tbl_MaterialRequest[Request Line Key (Helper)],tbl_MaterialRequest[Requesting Department])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="Request Priority (Ref)" dataDxfId="121">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="Request Priority (Ref)" dataDxfId="119">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Request Line Key (Helper)]],tbl_MaterialRequest[Request Line Key (Helper)],tbl_MaterialRequest[Request Priority])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="Quantity Requested (Ref)" dataDxfId="120">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="Quantity Requested (Ref)" dataDxfId="118">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Request Line Key (Helper)]],tbl_MaterialRequest[Request Line Key (Helper)],tbl_MaterialRequest[Quantity Requested])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="Pick Location " dataDxfId="119">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="Pick Location " dataDxfId="117">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Material Code]],tbl_PutAway[Material Code],tbl_PutAway[To Location])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0700-00000E000000}" name="Available Stock" dataDxfId="118">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0700-00000E000000}" name="Available Stock" dataDxfId="116">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Material Code]],'10_Stock_Card'!F4:F32,'10_Stock_Card'!M4:M32,"",0,-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="Quantity Picked" dataDxfId="117"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0700-000011000000}" name="Pick Status" dataDxfId="116">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="Quantity Picked" dataDxfId="115"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0700-000011000000}" name="Pick Status" dataDxfId="114">
       <calculatedColumnFormula>IF(tbl_PickingList[[#This Row],[Quantity Requested (Ref)]]=0,"Not Picked",IF(tbl_PickingList[[#This Row],[Quantity Picked]]&lt;tbl_PickingList[[#This Row],[Quantity Requested (Ref)]],"Partially Picked","Fully Picked"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{73D8D924-0876-4F34-9DBA-39EA7F81708E}" name="Picker" dataDxfId="115"/>
+    <tableColumn id="25" xr3:uid="{73D8D924-0876-4F34-9DBA-39EA7F81708E}" name="Picker" dataDxfId="113"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0700-000013000000}" name="Remarks"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0700-000014000000}" name="Pick Line Key (Helper)">
       <calculatedColumnFormula>tbl_PickingList[[#This Row],[Pick Number]]&amp;"-"&amp;tbl_PickingList[[#This Row],[Pick Line]]</calculatedColumnFormula>
@@ -5710,13 +5710,13 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="GI Date"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Pick Number"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="Pick Line"/>
-    <tableColumn id="19" xr3:uid="{E93C14AF-94CF-4F14-81CC-82A7578004AD}" name="Request Number" dataDxfId="114">
+    <tableColumn id="19" xr3:uid="{E93C14AF-94CF-4F14-81CC-82A7578004AD}" name="Request Number" dataDxfId="112">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],tbl_PickingList[Pick Line Key (Helper)],tbl_PickingList[Request Number])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{38A75A8A-6A06-4489-86DF-2EE0CE3971EF}" name="Request Line" dataDxfId="113">
+    <tableColumn id="20" xr3:uid="{38A75A8A-6A06-4489-86DF-2EE0CE3971EF}" name="Request Line" dataDxfId="111">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],tbl_PickingList[Pick Line Key (Helper)],tbl_PickingList[Request Line])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Pick Line Key (Helper)" dataDxfId="112">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Pick Line Key (Helper)" dataDxfId="110">
       <calculatedColumnFormula>D4&amp;"-"&amp;E4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="Material Code">
@@ -5725,32 +5725,32 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="Material Description">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Material Description])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="Base UoM" dataDxfId="111">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="Base UoM" dataDxfId="109">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="Issuing Location (Ref)" dataDxfId="110">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="Issuing Location (Ref)" dataDxfId="108">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],tbl_PickingList[Pick Line Key (Helper)],tbl_PickingList[[Pick Location ]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0800-00000B000000}" name="Requesting Department (Ref)" dataDxfId="109">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0800-00000B000000}" name="Requesting Department (Ref)" dataDxfId="107">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],tbl_PickingList[Pick Line Key (Helper)],tbl_PickingList[Requesting Department (Ref)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0800-00000C000000}" name="Quantity Picked (Ref)" dataDxfId="108">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0800-00000C000000}" name="Quantity Picked (Ref)" dataDxfId="106">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_GoodsIssue[[#This Row],[Pick Line Key (Helper)]],tbl_PickingList[Pick Line Key (Helper)],tbl_PickingList[Quantity Picked])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0800-00000D000000}" name="Quantity Issued"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0800-00000E000000}" name="Issue Variance" dataDxfId="107">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0800-00000E000000}" name="Issue Variance" dataDxfId="105">
       <calculatedColumnFormula>tbl_GoodsIssue[[#This Row],[Quantity Issued]]-tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{604A2A6F-C4DD-4034-9B7B-D193996479E5}" name="Issue Status" dataDxfId="106">
+    <tableColumn id="15" xr3:uid="{604A2A6F-C4DD-4034-9B7B-D193996479E5}" name="Issue Status" dataDxfId="104">
       <calculatedColumnFormula>IF(tbl_GoodsIssue[[#This Row],[Quantity Issued]]&lt;tbl_GoodsIssue[[#This Row],[Quantity Picked (Ref)]],"Partial","Completed")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{90D76B52-520C-4D83-81A3-B6E72FB0F149}" name="Issued By" dataDxfId="105"/>
-    <tableColumn id="22" xr3:uid="{76096732-D4A3-4A12-8DD0-430477B5B0BF}" name="Received By" dataDxfId="104"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0800-000010000000}" name="Remarks" dataDxfId="103"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0800-000011000000}" name="GI Line Key (Helper)" dataDxfId="102">
+    <tableColumn id="21" xr3:uid="{90D76B52-520C-4D83-81A3-B6E72FB0F149}" name="Issued By" dataDxfId="103"/>
+    <tableColumn id="22" xr3:uid="{76096732-D4A3-4A12-8DD0-430477B5B0BF}" name="Received By" dataDxfId="102"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0800-000010000000}" name="Remarks" dataDxfId="101"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0800-000011000000}" name="GI Line Key (Helper)" dataDxfId="100">
       <calculatedColumnFormula>tbl_GoodsIssue[[#This Row],[GI Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[GI Line]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{21F1F36F-2396-482F-BFCE-12F60C905BC9}" name="MR" dataDxfId="101">
+    <tableColumn id="23" xr3:uid="{21F1F36F-2396-482F-BFCE-12F60C905BC9}" name="MR" dataDxfId="99">
       <calculatedColumnFormula>tbl_GoodsIssue[[#This Row],[Request Number]]&amp;"-"&amp;tbl_GoodsIssue[[#This Row],[Request Line]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5940,21 +5940,21 @@
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.28515625" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" customWidth="1"/>
     <col min="11" max="11" width="10.42578125" customWidth="1"/>
     <col min="12" max="12" width="10.85546875" customWidth="1"/>
     <col min="13" max="13" width="10.5703125" customWidth="1"/>
     <col min="14" max="14" width="9.140625" customWidth="1"/>
-    <col min="15" max="15" width="27.140625" customWidth="1"/>
+    <col min="15" max="15" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -6949,42 +6949,42 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A31:E53">
-    <cfRule type="expression" dxfId="86" priority="105">
+    <cfRule type="expression" dxfId="84" priority="105">
       <formula>$E31="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="106">
+    <cfRule type="expression" dxfId="83" priority="106">
       <formula>#REF!="Critical Spare"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:J23 M4:O23">
-    <cfRule type="expression" dxfId="84" priority="30">
+    <cfRule type="expression" dxfId="82" priority="30">
       <formula>$N4="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="31">
+    <cfRule type="expression" dxfId="81" priority="31">
       <formula>$I4="Critical Spare"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:O30 A54:O498">
-    <cfRule type="expression" dxfId="82" priority="22">
+    <cfRule type="expression" dxfId="80" priority="22">
       <formula>$O24="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="23">
+    <cfRule type="expression" dxfId="79" priority="23">
       <formula>$I24="Critical Spare"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F23">
-    <cfRule type="duplicateValues" dxfId="80" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23">
-    <cfRule type="containsText" dxfId="79" priority="3" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="77" priority="3" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",H4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:L23">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="76" priority="1">
       <formula>$N4="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="75" priority="2">
       <formula>$I4="Critical Spare"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="J16" s="12">
         <f>IF(B16="Goods Receipt",_xlfn.XLOOKUP('10_Stock_Card'!E16,tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty]),0)</f>
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="K16" s="12">
         <f>IF(B16="Goods Issue",_xlfn.XLOOKUP(E16,tbl_GoodsIssue[GI Line Key (Helper)],tbl_GoodsIssue[Quantity Issued]),0)</f>
@@ -7802,11 +7802,11 @@
       </c>
       <c r="L16" s="93">
         <f t="shared" si="0"/>
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="M16" s="19">
         <f>SUMIFS($L$4:L16,$F$4:F16,F16)</f>
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="N16" s="6"/>
     </row>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="M21" s="19">
         <f>SUMIFS($L$4:L21,$F$4:F21,F21)</f>
-        <v>284</v>
+        <v>134</v>
       </c>
       <c r="N21" s="6"/>
     </row>
@@ -9002,33 +9002,33 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="A33:A39 A41:A518">
-    <cfRule type="expression" dxfId="22" priority="2">
+    <cfRule type="expression" dxfId="18" priority="2">
       <formula>$A33="Receipt"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="3">
+    <cfRule type="expression" dxfId="17" priority="3">
       <formula>$A33="Issue"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:B32">
-    <cfRule type="expression" dxfId="20" priority="5">
+    <cfRule type="expression" dxfId="16" priority="5">
       <formula>$B4="Goods Receipt"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="6">
+    <cfRule type="expression" dxfId="15" priority="6">
       <formula>$B4="Goods Issue"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L32">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>$L4&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L33:L518">
-    <cfRule type="expression" dxfId="17" priority="4">
+    <cfRule type="expression" dxfId="13" priority="4">
       <formula>$L33&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:M32">
-    <cfRule type="expression" dxfId="16" priority="7">
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>$M4&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9459,18 +9459,18 @@
       </c>
       <c r="H8" s="12">
         <f>_xlfn.XLOOKUP(tbl_CycleCount[[#This Row],[Material Code]],'10_Stock_Card'!F8:F36,'10_Stock_Card'!M8:M36,"",,-1)</f>
-        <v>284</v>
+        <v>134</v>
       </c>
       <c r="I8" s="11">
         <v>284</v>
       </c>
       <c r="J8" s="101">
         <f>tbl_CycleCount[[#This Row],[Physical Count]]-tbl_CycleCount[[#This Row],[System Qty (Ref)]]</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="K8" s="13">
         <f>IFERROR(tbl_CycleCount[[#This Row],[Variance (Qty)]]/tbl_CycleCount[[#This Row],[System Qty (Ref)]],0)</f>
-        <v>0</v>
+        <v>1.1194029850746268</v>
       </c>
       <c r="L8" s="106">
         <f>_xlfn.XLOOKUP(tbl_CycleCount[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Standard Cost (per Base UoM)])</f>
@@ -9478,11 +9478,11 @@
       </c>
       <c r="M8" s="107">
         <f>tbl_CycleCount[[#This Row],[Variance (Qty)]]*tbl_CycleCount[[#This Row],[Unit Cost (Ref)]]</f>
-        <v>0</v>
+        <v>57000000</v>
       </c>
       <c r="N8" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>Match</v>
+        <v>Overage</v>
       </c>
       <c r="O8" s="14" t="s">
         <v>320</v>
@@ -9740,50 +9740,50 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A24:A47">
-    <cfRule type="expression" dxfId="15" priority="117">
+    <cfRule type="expression" dxfId="11" priority="117">
       <formula>#REF!="Shortage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="118">
+    <cfRule type="expression" dxfId="10" priority="118">
       <formula>#REF!="Overage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="119">
+    <cfRule type="expression" dxfId="9" priority="119">
       <formula>#REF!="Match"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:D47">
-    <cfRule type="expression" dxfId="12" priority="121">
+    <cfRule type="expression" dxfId="8" priority="121">
       <formula>$C24="Under Investigation"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:O23 M48:O504">
-    <cfRule type="expression" dxfId="11" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>$M12="Shortage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>$M12="Overage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$M12="Match"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:P11">
-    <cfRule type="expression" dxfId="8" priority="110">
+    <cfRule type="expression" dxfId="4" priority="110">
       <formula>$N4="Shortage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="111">
+    <cfRule type="expression" dxfId="3" priority="111">
       <formula>$N4="Overage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="112">
+    <cfRule type="expression" dxfId="2" priority="112">
       <formula>$N4="Match"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12:R23 Q48:R504">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="1" priority="6">
       <formula>$Q12="Under Investigation"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4:R11 T4:T11">
-    <cfRule type="expression" dxfId="4" priority="113">
+    <cfRule type="expression" dxfId="0" priority="113">
       <formula>$R4="Under Investigation"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10342,15 +10342,15 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A4:I13">
-    <cfRule type="expression" dxfId="78" priority="37">
+    <cfRule type="expression" dxfId="74" priority="37">
       <formula>$I4="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="38">
+    <cfRule type="expression" dxfId="73" priority="38">
       <formula>$H4="Preferred"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H21">
-    <cfRule type="expression" dxfId="76" priority="7">
+    <cfRule type="expression" dxfId="72" priority="7">
       <formula>$H14="Under Review"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11296,36 +11296,36 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A29:G36 A46:B55 A56:G512">
-    <cfRule type="expression" dxfId="75" priority="2">
+    <cfRule type="expression" dxfId="71" priority="2">
       <formula>$G29="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="3">
+    <cfRule type="expression" dxfId="70" priority="3">
       <formula>$D29="Hazardous"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:H15 A16:F17 H16:H17 A18:H28">
-    <cfRule type="expression" dxfId="73" priority="41">
+    <cfRule type="expression" dxfId="69" priority="41">
       <formula>$H4="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="42">
+    <cfRule type="expression" dxfId="68" priority="42">
       <formula>$E4="Hazardous"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29:E36 E56:E512">
-    <cfRule type="expression" dxfId="71" priority="4">
+    <cfRule type="expression" dxfId="67" priority="4">
       <formula>$E29="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F28">
-    <cfRule type="expression" dxfId="70" priority="46">
+    <cfRule type="expression" dxfId="66" priority="46">
       <formula>$F4="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G16">
-    <cfRule type="expression" dxfId="69" priority="105">
+    <cfRule type="expression" dxfId="65" priority="105">
       <formula>$H17="Inactive"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="106">
+    <cfRule type="expression" dxfId="64" priority="106">
       <formula>$E17="Hazardous"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12760,14 +12760,14 @@
         <v>45</v>
       </c>
       <c r="I23" s="11">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="J23" s="33">
         <v>375000</v>
       </c>
       <c r="K23" s="31">
         <f>tbl_PurchaseOrder[[#This Row],[Ordered Qty]]*J23</f>
-        <v>108750000</v>
+        <v>52500000</v>
       </c>
       <c r="L23" s="14" t="s">
         <v>19</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="O23" s="3">
         <f>SUMIFS(tbl_GoodsReceipt[Received Qty],tbl_GoodsReceipt[PO Line Key (Helper)],tbl_PurchaseOrder[[#This Row],[PO Line Key (Helper)]])</f>
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="P23" s="103">
         <f>IFERROR(tbl_PurchaseOrder[[#This Row],[Received Qty]]-tbl_PurchaseOrder[[#This Row],[Ordered Qty]],0)</f>
@@ -13196,53 +13196,53 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="C33:C79">
-    <cfRule type="expression" dxfId="67" priority="127">
+    <cfRule type="expression" dxfId="63" priority="127">
       <formula>$C33="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33:G79">
-    <cfRule type="expression" dxfId="66" priority="131">
+    <cfRule type="expression" dxfId="62" priority="131">
       <formula>$G33="Cancelled"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="132">
+    <cfRule type="expression" dxfId="61" priority="132">
       <formula>$G33="Closed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="133">
+    <cfRule type="expression" dxfId="60" priority="133">
       <formula>$G33="Open"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L26 L28:L29">
-    <cfRule type="expression" dxfId="63" priority="56">
+    <cfRule type="expression" dxfId="59" priority="56">
       <formula>$L4="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N30:N32 N80:N515">
-    <cfRule type="expression" dxfId="62" priority="3">
+    <cfRule type="expression" dxfId="58" priority="3">
       <formula>$N30="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q26 Q28:Q29">
-    <cfRule type="expression" dxfId="61" priority="1">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>$Q4="Partial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="64">
+    <cfRule type="expression" dxfId="56" priority="64">
       <formula>$Q4="Cancelled"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="65">
+    <cfRule type="expression" dxfId="55" priority="65">
       <formula>$Q4="Closed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="66">
+    <cfRule type="expression" dxfId="54" priority="66">
       <formula>$Q4="Open"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R30:R32 R80:R515">
-    <cfRule type="expression" dxfId="57" priority="4">
+    <cfRule type="expression" dxfId="53" priority="4">
       <formula>$R30="Cancelled"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="5">
+    <cfRule type="expression" dxfId="52" priority="5">
       <formula>$R30="Closed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="6">
+    <cfRule type="expression" dxfId="51" priority="6">
       <formula>$R30="Open"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="K14" s="12">
         <f>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Ordered Qty])</f>
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="L14" s="12" t="str">
         <f>_xlfn.XLOOKUP(tbl_GoodsReceipt[[#This Row],[PO Line Key (Helper)]],tbl_PurchaseOrder[PO Line Key (Helper)],tbl_PurchaseOrder[Purchase UoM])</f>
@@ -14502,10 +14502,10 @@
         <v>435</v>
       </c>
       <c r="R14" s="11">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="S14" s="11">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="T14" s="19">
         <f>tbl_GoodsReceipt[[#This Row],[Received Qty]]-tbl_GoodsReceipt[[#This Row],[Accepted Qty]]</f>
@@ -15248,7 +15248,7 @@
       <c r="I36" s="22"/>
       <c r="J36" s="27"/>
       <c r="K36" s="27">
-        <v>330</v>
+        <v>180</v>
       </c>
       <c r="L36" s="22"/>
       <c r="M36" s="22"/>
@@ -15477,31 +15477,31 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="K24:K35">
-    <cfRule type="expression" dxfId="54" priority="124">
+    <cfRule type="expression" dxfId="50" priority="124">
       <formula>$K24="Fully Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="125">
+    <cfRule type="expression" dxfId="49" priority="125">
       <formula>$K24="Partially Accepted"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S22:S23 S36:S512">
-    <cfRule type="expression" dxfId="52" priority="6">
+    <cfRule type="expression" dxfId="48" priority="6">
       <formula>$S22="Fully Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="7">
+    <cfRule type="expression" dxfId="47" priority="7">
       <formula>$S22="Partially Accepted"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4:U21">
-    <cfRule type="expression" dxfId="50" priority="61">
+    <cfRule type="expression" dxfId="46" priority="61">
       <formula>$U4="Fully Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="62">
+    <cfRule type="expression" dxfId="45" priority="62">
       <formula>$U4="Partially Accepted"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:Z21">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>$Z4="Late"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16560,14 +16560,14 @@
       </c>
       <c r="K14" s="12">
         <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Accepted Qty])</f>
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="L14" s="12" t="str">
         <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[GR Line Key (Helper)]],tbl_GoodsReceipt[GR Line Key (Helper)],tbl_GoodsReceipt[Purchase UoM])</f>
         <v>KG</v>
       </c>
       <c r="M14" s="7">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="N14" s="12" t="str">
         <f>_xlfn.XLOOKUP(tbl_PutAway[[#This Row],[Material Code]],tbl_MasterMaterial[Material Code],tbl_MasterMaterial[Base UoM])</f>
@@ -17330,26 +17330,26 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="Q22:Q513">
-    <cfRule type="expression" dxfId="47" priority="5">
+    <cfRule type="expression" dxfId="43" priority="5">
       <formula>$Q22="Mismatch - Review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4:R20">
-    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:T20">
-    <cfRule type="expression" dxfId="45" priority="2">
+    <cfRule type="expression" dxfId="41" priority="2">
       <formula>$T4="Mismatch - Review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4:U20">
-    <cfRule type="expression" dxfId="44" priority="3">
+    <cfRule type="expression" dxfId="40" priority="3">
       <formula>$U4="Partial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="74">
+    <cfRule type="expression" dxfId="39" priority="74">
       <formula>$U4="Exception - Needs Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="75">
+    <cfRule type="expression" dxfId="38" priority="75">
       <formula>$U4="Completed"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17848,7 +17848,7 @@
       </c>
       <c r="L9" s="19">
         <f>_xlfn.XLOOKUP(tbl_MaterialRequest[[#This Row],[Material Code]],'10_Stock_Card'!F9:F40,'10_Stock_Card'!M9:M40,"",0,-1)</f>
-        <v>284</v>
+        <v>134</v>
       </c>
       <c r="M9" s="16" t="str">
         <f t="shared" si="0"/>
@@ -18432,28 +18432,28 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="I19:I507">
-    <cfRule type="expression" dxfId="41" priority="2">
+    <cfRule type="expression" dxfId="37" priority="2">
       <formula>$I19="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K18">
-    <cfRule type="expression" dxfId="40" priority="83">
+    <cfRule type="expression" dxfId="36" priority="83">
       <formula>$K4="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N18">
-    <cfRule type="expression" dxfId="39" priority="80">
+    <cfRule type="expression" dxfId="35" priority="80">
       <formula>$M4="Insufficient - Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="81">
+    <cfRule type="expression" dxfId="34" priority="81">
       <formula>$M4="Sufficient"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:N507">
-    <cfRule type="expression" dxfId="37" priority="3">
+    <cfRule type="expression" dxfId="33" priority="3">
       <formula>$N19="Insufficient - Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="4">
+    <cfRule type="expression" dxfId="32" priority="4">
       <formula>$N19="Sufficient"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18935,7 +18935,7 @@
       </c>
       <c r="N8" s="97">
         <f>_xlfn.XLOOKUP(tbl_PickingList[[#This Row],[Material Code]],'10_Stock_Card'!F8:F36,'10_Stock_Card'!M8:M36,"",0,-1)</f>
-        <v>284</v>
+        <v>134</v>
       </c>
       <c r="O8" s="11">
         <v>6</v>
@@ -19455,31 +19455,31 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="K4:K18 K80:K507">
-    <cfRule type="expression" dxfId="35" priority="2">
+    <cfRule type="expression" dxfId="31" priority="2">
       <formula>$K4="Urgent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:P15">
-    <cfRule type="expression" dxfId="34" priority="88">
+    <cfRule type="expression" dxfId="30" priority="88">
       <formula>$P4="Fully Picked"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:Q15">
-    <cfRule type="expression" dxfId="33" priority="87">
+    <cfRule type="expression" dxfId="29" priority="87">
       <formula>$P4="Partially Picked"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="89">
+    <cfRule type="expression" dxfId="28" priority="89">
       <formula>$P4="Not Picked"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q16:Q17 Q80:Q507">
-    <cfRule type="expression" dxfId="31" priority="4">
+    <cfRule type="expression" dxfId="27" priority="4">
       <formula>$Q16="Partially Picked"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="5">
+    <cfRule type="expression" dxfId="26" priority="5">
       <formula>$Q16="Fully Picked"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="6">
+    <cfRule type="expression" dxfId="25" priority="6">
       <formula>$Q16="Not Picked"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20781,32 +20781,32 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="P4:Q15">
-    <cfRule type="expression" dxfId="28" priority="92">
+    <cfRule type="expression" dxfId="24" priority="92">
       <formula>$P4&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q15">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>$Q4="Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:S15">
-    <cfRule type="expression" dxfId="26" priority="95">
+    <cfRule type="expression" dxfId="22" priority="95">
       <formula>#REF!&lt;&gt;"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q16:S16 O17:Q28 Q29:S507">
-    <cfRule type="expression" dxfId="25" priority="96">
+    <cfRule type="expression" dxfId="21" priority="96">
       <formula>#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R17:R28">
-    <cfRule type="expression" dxfId="24" priority="100">
+    <cfRule type="expression" dxfId="20" priority="100">
       <formula>$R17&lt;&gt;"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T16:U16 T29:U507">
-    <cfRule type="expression" dxfId="23" priority="4">
+    <cfRule type="expression" dxfId="19" priority="4">
       <formula>$T16&lt;&gt;"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
